--- a/results/job_matches_2026-09-15.xlsx
+++ b/results/job_matches_2026-09-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G187"/>
+  <dimension ref="A1:G208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,35 +468,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Engineer III - Databricks</t>
+          <t>Data Architect - Irving</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.8</v>
+        <v>20.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, ECS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98c558c6b0a21fef</t>
+          <t>https://www.indeed.com/viewjob?jk=bbe7b157eada5171</t>
         </is>
       </c>
     </row>
@@ -608,17 +608,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Telemetry Data Infrastructure DevOps Software Engineer III</t>
+          <t>Senior Databrick Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>TradeWind Services</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Richland, WA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c634a2ea8b0b5dc</t>
+          <t>https://www.indeed.com/viewjob?jk=53e3a08c1c44bf91</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Engineer - Hyperscale Analytics</t>
+          <t>Telemetry Data Infrastructure DevOps Software Engineer III</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Veeam Software</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, HDFS, Spark, Scala</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f17632f11610e0ed</t>
+          <t>https://www.indeed.com/viewjob?jk=8c634a2ea8b0b5dc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr. AI Data Engineer</t>
+          <t>Senior Engineer - Hyperscale Analytics</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Park Place Technologies</t>
+          <t>Veeam Software</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Highland Heights, OH, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Dataflow, Hadoop, Spark, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, HDFS, Spark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e8be741f2af4076</t>
+          <t>https://www.indeed.com/viewjob?jk=f17632f11610e0ed</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Infrastructure DevOps Software Engineer III</t>
+          <t>Sr. AI Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Park Place Technologies</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Highland Heights, OH, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Dataflow, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c736424a6d7924ca</t>
+          <t>https://www.indeed.com/viewjob?jk=1e8be741f2af4076</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr. DevSecOps Engineer</t>
+          <t>Infrastructure DevOps Software Engineer III</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>EBSCO Information Services</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7fe85eb12d0cac3</t>
+          <t>https://www.indeed.com/viewjob?jk=c736424a6d7924ca</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Engineer</t>
+          <t>Senior Azure Data Architect</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BCD</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Wilmington, NC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Scala, CI/CD</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Medallion Architecture, Spark, PySpark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d22b7b216664062</t>
+          <t>https://www.indeed.com/viewjob?jk=7608d5894436a65d</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>EBSCO Information Services</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, Databricks, Medallion Architecture, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a91e83e2437ff07f</t>
+          <t>https://www.indeed.com/viewjob?jk=b7fe85eb12d0cac3</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer-1</t>
+          <t>Data Integration Engineer II</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>mPulse</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, Scala, PostgreSQL, DynamoDB</t>
+          <t>AWS, Redshift, S3, Scala, Snowflake, SQL Server, PostgreSQL, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27628c1d7944c002</t>
+          <t>https://www.indeed.com/viewjob?jk=38b79b27689fa7f5</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data Databricks, Python / Java</t>
+          <t>Data Integration Engineer II</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>mPulse</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.2</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Redshift, S3, Scala, Snowflake, SQL Server, PostgreSQL, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76a3f3303ca4a1e8</t>
+          <t>https://www.indeed.com/viewjob?jk=b3463838e828923f</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Life Sciences.AI</t>
+          <t>Senior AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>BCD</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.2</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, GCP, BigQuery, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a2b7a80aec3b5d1</t>
+          <t>https://www.indeed.com/viewjob?jk=4d22b7b216664062</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer II (Full Stack)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Kafka, DynamoDB</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d6a3b442efcc911</t>
+          <t>https://www.indeed.com/viewjob?jk=262e7b6fb0562f09</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Core specialty</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, GCP, Scala, Snowflake, Data Modeling, ELT</t>
+          <t>AWS, Glue, EMR, S3, Databricks, Medallion Architecture, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7398d2f9ab83a441</t>
+          <t>https://www.indeed.com/viewjob?jk=a91e83e2437ff07f</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Java Full Stack Developer-1</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Core specialty</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, GCP, Scala, Snowflake, Data Modeling, ELT</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, Scala, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b44d832238c13ae8</t>
+          <t>https://www.indeed.com/viewjob?jk=27628c1d7944c002</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Software Engineer III - Big Data Databricks, Python / Java</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>clickhouse</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fa44fdea0190b34</t>
+          <t>https://www.indeed.com/viewjob?jk=76a3f3303ca4a1e8</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer III - PySpark/AWS/Databricks</t>
+          <t>Senior Data Engineer - Life Sciences.AI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, CI/CD, Airflow</t>
+          <t>AWS, IAM, Azure, Databricks, GCP, BigQuery, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12b2d3a25dd65381</t>
+          <t>https://www.indeed.com/viewjob?jk=6a2b7a80aec3b5d1</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Developer-Information Services Senior</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Indiana University Health</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afda63d4c955805b</t>
+          <t>https://www.indeed.com/viewjob?jk=2d6a3b442efcc911</t>
         </is>
       </c>
     </row>
@@ -1173,20 +1173,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Hylant</t>
+          <t>Core specialty</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, GCP, Scala, Snowflake, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8820ee81d8c77a67</t>
+          <t>https://www.indeed.com/viewjob?jk=7398d2f9ab83a441</t>
         </is>
       </c>
     </row>
@@ -1208,20 +1208,20 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Hylant</t>
+          <t>Core specialty</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Carmel, IN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, GCP, Scala, Snowflake, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fb4b4b353eb8bc7</t>
+          <t>https://www.indeed.com/viewjob?jk=b44d832238c13ae8</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Hylant</t>
+          <t>clickhouse</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09c607a8a6e9e6e1</t>
+          <t>https://www.indeed.com/viewjob?jk=7fa44fdea0190b34</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer III - PySpark/AWS/Databricks</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Hylant</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00deb545cdf8539e</t>
+          <t>https://www.indeed.com/viewjob?jk=12b2d3a25dd65381</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Developer-Information Services Senior</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Hylant</t>
+          <t>Indiana University Health</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f436c35b9293c1bb</t>
+          <t>https://www.indeed.com/viewjob?jk=afda63d4c955805b</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Fort Wayne, IN, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42fde78a8e52a847</t>
+          <t>https://www.indeed.com/viewjob?jk=8820ee81d8c77a67</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Carmel, IN, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93f331567a1b25da</t>
+          <t>https://www.indeed.com/viewjob?jk=0fb4b4b353eb8bc7</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ecdb7549167f466</t>
+          <t>https://www.indeed.com/viewjob?jk=09c607a8a6e9e6e1</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Independence, OH, US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0157f56a6e27cad5</t>
+          <t>https://www.indeed.com/viewjob?jk=00deb545cdf8539e</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Bloomington, IN, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ced0409c76f4850</t>
+          <t>https://www.indeed.com/viewjob?jk=f436c35b9293c1bb</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>Fort Wayne, IN, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f97eb4b6c78e57e1</t>
+          <t>https://www.indeed.com/viewjob?jk=42fde78a8e52a847</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=080ed824e7309c6d</t>
+          <t>https://www.indeed.com/viewjob?jk=93f331567a1b25da</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e9941187a535d8b</t>
+          <t>https://www.indeed.com/viewjob?jk=1ecdb7549167f466</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Findlay, OH, US USA</t>
+          <t>Independence, OH, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26792be3f1ce7d82</t>
+          <t>https://www.indeed.com/viewjob?jk=0157f56a6e27cad5</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>Bloomington, IN, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40097b188627fc8f</t>
+          <t>https://www.indeed.com/viewjob?jk=1ced0409c76f4850</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=438fab27a54b95e5</t>
+          <t>https://www.indeed.com/viewjob?jk=f97eb4b6c78e57e1</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c6e53394ba3aa7e</t>
+          <t>https://www.indeed.com/viewjob?jk=080ed824e7309c6d</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e32d13892fbf579</t>
+          <t>https://www.indeed.com/viewjob?jk=0e9941187a535d8b</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Findlay, OH, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c82bfdcacec2b79</t>
+          <t>https://www.indeed.com/viewjob?jk=26792be3f1ce7d82</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18104515e179e7ed</t>
+          <t>https://www.indeed.com/viewjob?jk=40097b188627fc8f</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Dunwoody, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d522390ab1db0241</t>
+          <t>https://www.indeed.com/viewjob?jk=438fab27a54b95e5</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ad72ad30f1ab368</t>
+          <t>https://www.indeed.com/viewjob?jk=7c6e53394ba3aa7e</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Carolina, PR, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be64c2d5635296ce</t>
+          <t>https://www.indeed.com/viewjob?jk=2e32d13892fbf579</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f694fd137783bdde</t>
+          <t>https://www.indeed.com/viewjob?jk=8c82bfdcacec2b79</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=299f65eca357474b</t>
+          <t>https://www.indeed.com/viewjob?jk=18104515e179e7ed</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>Dunwoody, GA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78155475e0b7db74</t>
+          <t>https://www.indeed.com/viewjob?jk=d522390ab1db0241</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fc3e569ad89e0eb</t>
+          <t>https://www.indeed.com/viewjob?jk=3ad72ad30f1ab368</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>Carolina, PR, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=614cf434248f98f7</t>
+          <t>https://www.indeed.com/viewjob?jk=be64c2d5635296ce</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2629ad6556cbacf4</t>
+          <t>https://www.indeed.com/viewjob?jk=f694fd137783bdde</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8218cb998a5c0151</t>
+          <t>https://www.indeed.com/viewjob?jk=299f65eca357474b</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01de0a106d50019f</t>
+          <t>https://www.indeed.com/viewjob?jk=78155475e0b7db74</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Carolina, PR, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a08ea81549a22f9</t>
+          <t>https://www.indeed.com/viewjob?jk=4fc3e569ad89e0eb</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56c3823d88792143</t>
+          <t>https://www.indeed.com/viewjob?jk=614cf434248f98f7</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a55c291dace4b53</t>
+          <t>https://www.indeed.com/viewjob?jk=2629ad6556cbacf4</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b3cff0ccd0ca269</t>
+          <t>https://www.indeed.com/viewjob?jk=8218cb998a5c0151</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fae7a2c2e6e1358</t>
+          <t>https://www.indeed.com/viewjob?jk=01de0a106d50019f</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Carolina, PR, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=016a658dc9ac3489</t>
+          <t>https://www.indeed.com/viewjob?jk=6a08ea81549a22f9</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc0d0f1f18eb8438</t>
+          <t>https://www.indeed.com/viewjob?jk=56c3823d88792143</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47971bbc08557e3c</t>
+          <t>https://www.indeed.com/viewjob?jk=1a55c291dace4b53</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bfcc94d4b3f34a6</t>
+          <t>https://www.indeed.com/viewjob?jk=1b3cff0ccd0ca269</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f49f733f65d11ed</t>
+          <t>https://www.indeed.com/viewjob?jk=7fae7a2c2e6e1358</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8330457e7c7d4248</t>
+          <t>https://www.indeed.com/viewjob?jk=016a658dc9ac3489</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f90aa460666eb778</t>
+          <t>https://www.indeed.com/viewjob?jk=dc0d0f1f18eb8438</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6701998be316239a</t>
+          <t>https://www.indeed.com/viewjob?jk=47971bbc08557e3c</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d920562d203a185e</t>
+          <t>https://www.indeed.com/viewjob?jk=7bfcc94d4b3f34a6</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8aa55866530a52ff</t>
+          <t>https://www.indeed.com/viewjob?jk=3f49f733f65d11ed</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a565c5a09573c96</t>
+          <t>https://www.indeed.com/viewjob?jk=8330457e7c7d4248</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Birmingham, MI, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea61995aa36120f0</t>
+          <t>https://www.indeed.com/viewjob?jk=f90aa460666eb778</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=885e1f5bffaa36a1</t>
+          <t>https://www.indeed.com/viewjob?jk=6701998be316239a</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Dublin, OH, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77ba46a2cdbcf8ec</t>
+          <t>https://www.indeed.com/viewjob?jk=d920562d203a185e</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0101e7a2a0fedfa2</t>
+          <t>https://www.indeed.com/viewjob?jk=8aa55866530a52ff</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=570dfe76b557e2f0</t>
+          <t>https://www.indeed.com/viewjob?jk=7a565c5a09573c96</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Elkhart, IN, US USA</t>
+          <t>Birmingham, MI, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d348ebc076adb84</t>
+          <t>https://www.indeed.com/viewjob?jk=ea61995aa36120f0</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98d25fbfe90fcd1b</t>
+          <t>https://www.indeed.com/viewjob?jk=885e1f5bffaa36a1</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Dublin, OH, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13b85db8861d59de</t>
+          <t>https://www.indeed.com/viewjob?jk=77ba46a2cdbcf8ec</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>HI, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ffc3524695bd37a</t>
+          <t>https://www.indeed.com/viewjob?jk=0101e7a2a0fedfa2</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09d343f340846bb1</t>
+          <t>https://www.indeed.com/viewjob?jk=570dfe76b557e2f0</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Toledo, OH, US USA</t>
+          <t>Elkhart, IN, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86fe5a29c6f478bb</t>
+          <t>https://www.indeed.com/viewjob?jk=8d348ebc076adb84</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a71a75a7a6f6ded</t>
+          <t>https://www.indeed.com/viewjob?jk=98d25fbfe90fcd1b</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4822d68866185d6</t>
+          <t>https://www.indeed.com/viewjob?jk=13b85db8861d59de</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>HI, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e8c551e853470e4</t>
+          <t>https://www.indeed.com/viewjob?jk=5ffc3524695bd37a</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7b3b740adef358e</t>
+          <t>https://www.indeed.com/viewjob?jk=09d343f340846bb1</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>Toledo, OH, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28bf28a64e288c3c</t>
+          <t>https://www.indeed.com/viewjob?jk=86fe5a29c6f478bb</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Engineer, Software (SWE) – GIA Platform</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Hylant</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e58133888b7ac460</t>
+          <t>https://www.indeed.com/viewjob?jk=8a71a75a7a6f6ded</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Platform Administrator (Databricks)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Nitka Technologies</t>
+          <t>Hylant</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, IAM, Databricks, Unity Catalog, Hive, Spark, Kafka, Time Travel</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,32 +3436,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=414be1be9d96afd0</t>
+          <t>https://www.indeed.com/viewjob?jk=b4822d68866185d6</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Software Engineer III - ML Model Delivery</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Hylant</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, ECS, RDS, Databricks, Spark, Scala, MLOps, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,32 +3471,32 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fc384810dc1e31d</t>
+          <t>https://www.indeed.com/viewjob?jk=1e8c551e853470e4</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Data Scientist – Healthcare Analytics</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>Hylant</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eeadc804a9484d0d</t>
+          <t>https://www.indeed.com/viewjob?jk=f7b3b740adef358e</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Data Scientist – Healthcare Analytics</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>Hylant</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,67 +3541,67 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a28368c599a0643</t>
+          <t>https://www.indeed.com/viewjob?jk=28bf28a64e288c3c</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Data Scientist – Healthcare Analytics</t>
+          <t>Senior Clinical Data Analyst (Healthcare Analytics)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>Tendo</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Richland, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
+          <t>AWS, Glue, EMR, Athena, S3, RDS, Azure, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=220fde5a7ab61250</t>
+          <t>https://www.indeed.com/viewjob?jk=ee930887aa7df056</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Data Scientist – Healthcare Analytics</t>
+          <t>Senior Engineer, Software (SWE) – GIA Platform</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, CI/CD</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,32 +3611,32 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34b1402bf6437dcd</t>
+          <t>https://www.indeed.com/viewjob?jk=e58133888b7ac460</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Data Scientist – Healthcare Analytics</t>
+          <t>Platform Administrator (Databricks)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>Nitka Technologies</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Clinton, MS, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
+          <t>AWS, S3, SQS, IAM, Databricks, Unity Catalog, Hive, Spark, Kafka, Time Travel</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,32 +3646,32 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f19c9e531ef55a20</t>
+          <t>https://www.indeed.com/viewjob?jk=414be1be9d96afd0</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Data Scientist – Healthcare Analytics</t>
+          <t>Engineer 1</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Fargo, ND, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c9e73c822f8844a</t>
+          <t>https://www.indeed.com/viewjob?jk=759a4cfd65b3309c</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Data Scientist – Healthcare Analytics</t>
+          <t>Software Engineer III - ML Model Delivery</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Annapolis, MD, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
+          <t>AWS, EMR, S3, ECS, RDS, Databricks, Spark, Scala, MLOps, Terraform</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85c7d84effba6226</t>
+          <t>https://www.indeed.com/viewjob?jk=8fc384810dc1e31d</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60c7d9e06cdaf076</t>
+          <t>https://www.indeed.com/viewjob?jk=eeadc804a9484d0d</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21f12a1ca162239a</t>
+          <t>https://www.indeed.com/viewjob?jk=9a28368c599a0643</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Liberty, MO, US USA</t>
+          <t>Richland, WA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d94a40eeb0b40c06</t>
+          <t>https://www.indeed.com/viewjob?jk=220fde5a7ab61250</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Newmarket, NH, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6294f6e595512d42</t>
+          <t>https://www.indeed.com/viewjob?jk=34b1402bf6437dcd</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Monrovia, CA, US USA</t>
+          <t>Clinton, MS, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=885e9edc1afd7aa4</t>
+          <t>https://www.indeed.com/viewjob?jk=f19c9e531ef55a20</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Fargo, ND, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25e0a7f11b2f5765</t>
+          <t>https://www.indeed.com/viewjob?jk=2c9e73c822f8844a</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Annapolis, MD, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80a579dae67397ca</t>
+          <t>https://www.indeed.com/viewjob?jk=85c7d84effba6226</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5feacfc39b3d5f9a</t>
+          <t>https://www.indeed.com/viewjob?jk=60c7d9e06cdaf076</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Newport, MI, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d8a52daee3e8452</t>
+          <t>https://www.indeed.com/viewjob?jk=21f12a1ca162239a</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Baton Rouge, LA, US USA</t>
+          <t>Liberty, MO, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0ed8e336465d87a</t>
+          <t>https://www.indeed.com/viewjob?jk=d94a40eeb0b40c06</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Newmarket, NH, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25a3d0fe6ce79647</t>
+          <t>https://www.indeed.com/viewjob?jk=6294f6e595512d42</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Medway, MA, US USA</t>
+          <t>Monrovia, CA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f686962a348d2f1d</t>
+          <t>https://www.indeed.com/viewjob?jk=885e9edc1afd7aa4</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Watson, AR, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4782d437ac23c24f</t>
+          <t>https://www.indeed.com/viewjob?jk=25e0a7f11b2f5765</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Marion, IA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4581f1a3af15cc3</t>
+          <t>https://www.indeed.com/viewjob?jk=80a579dae67397ca</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Hudson, WI, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ed08d422e18d838</t>
+          <t>https://www.indeed.com/viewjob?jk=5feacfc39b3d5f9a</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Newport, MI, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3d42ed3ce6788ed</t>
+          <t>https://www.indeed.com/viewjob?jk=7d8a52daee3e8452</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Barrington, RI, US USA</t>
+          <t>Baton Rouge, LA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54f7850a724e338c</t>
+          <t>https://www.indeed.com/viewjob?jk=d0ed8e336465d87a</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b45d9f24f862a12b</t>
+          <t>https://www.indeed.com/viewjob?jk=25a3d0fe6ce79647</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Tyler, TX, US USA</t>
+          <t>Medway, MA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=834a146cee4b0ee3</t>
+          <t>https://www.indeed.com/viewjob?jk=f686962a348d2f1d</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Frankfort, KY, US USA</t>
+          <t>Watson, AR, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66bfe8bbf500669f</t>
+          <t>https://www.indeed.com/viewjob?jk=4782d437ac23c24f</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Marion, IA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b8778237b3a9a9b</t>
+          <t>https://www.indeed.com/viewjob?jk=e4581f1a3af15cc3</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Honolulu, HI, US USA</t>
+          <t>Hudson, WI, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f5dfcba34d7a802</t>
+          <t>https://www.indeed.com/viewjob?jk=6ed08d422e18d838</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Dayton, MN, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32f10a5c826d77c3</t>
+          <t>https://www.indeed.com/viewjob?jk=f3d42ed3ce6788ed</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Barrington, RI, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1964898c1fe8582</t>
+          <t>https://www.indeed.com/viewjob?jk=54f7850a724e338c</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5340ba338a6dbdb</t>
+          <t>https://www.indeed.com/viewjob?jk=b45d9f24f862a12b</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Parlin, NJ, US USA</t>
+          <t>Tyler, TX, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04ad3829889eff15</t>
+          <t>https://www.indeed.com/viewjob?jk=834a146cee4b0ee3</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Derby, CT, US USA</t>
+          <t>Frankfort, KY, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee4a69c65915dae6</t>
+          <t>https://www.indeed.com/viewjob?jk=66bfe8bbf500669f</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb5879047bb49aa2</t>
+          <t>https://www.indeed.com/viewjob?jk=8b8778237b3a9a9b</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Honolulu, HI, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=736a88fef080818b</t>
+          <t>https://www.indeed.com/viewjob?jk=2f5dfcba34d7a802</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Dayton, MN, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4914aa2faa0a7d7e</t>
+          <t>https://www.indeed.com/viewjob?jk=32f10a5c826d77c3</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Provo, UT, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09950965e6e09286</t>
+          <t>https://www.indeed.com/viewjob?jk=c1964898c1fe8582</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc817f9191b34c97</t>
+          <t>https://www.indeed.com/viewjob?jk=b5340ba338a6dbdb</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Caldwell, ID, US USA</t>
+          <t>Parlin, NJ, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19ab03de0b3dc4f3</t>
+          <t>https://www.indeed.com/viewjob?jk=04ad3829889eff15</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Pierre, SD, US USA</t>
+          <t>Derby, CT, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b7ac807f2bfd018</t>
+          <t>https://www.indeed.com/viewjob?jk=ee4a69c65915dae6</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Rehoboth Beach, DE, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2998b67c6e643dc</t>
+          <t>https://www.indeed.com/viewjob?jk=cb5879047bb49aa2</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Stafford, VA, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ee0e59c6632733f</t>
+          <t>https://www.indeed.com/viewjob?jk=736a88fef080818b</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Palmer, AK, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a89b194674200ed2</t>
+          <t>https://www.indeed.com/viewjob?jk=4914aa2faa0a7d7e</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Provo, UT, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1e7316082fa5dfb</t>
+          <t>https://www.indeed.com/viewjob?jk=09950965e6e09286</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Missoula, MT, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=706b0b9e31c343c4</t>
+          <t>https://www.indeed.com/viewjob?jk=cc817f9191b34c97</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Caldwell, ID, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,24 +5116,24 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf9c2207875eb310</t>
+          <t>https://www.indeed.com/viewjob?jk=19ab03de0b3dc4f3</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Data Scientist – Healthcare Analytics</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Cotulla Education</t>
+          <t>Ensora Health</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>Pierre, SD, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=912b403391eebae1</t>
+          <t>https://www.indeed.com/viewjob?jk=6b7ac807f2bfd018</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Scientist – Healthcare Analytics</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Vforce Infotech</t>
+          <t>Ensora Health</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Rehoboth Beach, DE, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,24 +5186,24 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a4124e344d24526</t>
+          <t>https://www.indeed.com/viewjob?jk=f2998b67c6e643dc</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Data Scientist – Healthcare Analytics</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Ensora Health</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Stafford, VA, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, EMR, Athena, S3, Databricks, Spark, Scala, Snowflake, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,24 +5221,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30987ecce424f169</t>
+          <t>https://www.indeed.com/viewjob?jk=1ee0e59c6632733f</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Senior Cloud Infrastructure Engineer</t>
+          <t>Senior Data Scientist – Healthcare Analytics</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Ｃollective</t>
+          <t>Ensora Health</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Palmer, AK, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, GCP, BigQuery, Scala, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,24 +5256,24 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57341d2f2afa0500</t>
+          <t>https://www.indeed.com/viewjob?jk=a89b194674200ed2</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Data Scientist – Healthcare Analytics</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Smile Partners USA</t>
+          <t>Ensora Health</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Troy, MI, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,34 +5281,34 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42652418f10ddaf6</t>
+          <t>https://www.indeed.com/viewjob?jk=e1e7316082fa5dfb</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Identity</t>
+          <t>Senior Data Scientist – Healthcare Analytics</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Zeta Global</t>
+          <t>Ensora Health</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Missoula, MT, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, Hive, Spark, Scala, Kafka, Snowflake, NoSQL, Data Modeling, ELT, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2626f31a8519115</t>
+          <t>https://www.indeed.com/viewjob?jk=706b0b9e31c343c4</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Identity</t>
+          <t>Senior Data Scientist – Healthcare Analytics</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Zeta Global</t>
+          <t>Ensora Health</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, Hive, Spark, Scala, Kafka, Snowflake, NoSQL, Data Modeling, ELT, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8127a1fdd36b3f92</t>
+          <t>https://www.indeed.com/viewjob?jk=cf9c2207875eb310</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Identity</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Zeta Global</t>
+          <t>Cotulla Education</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, Hive, Spark, Scala, Kafka, Snowflake, NoSQL, Data Modeling, ELT, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0c452b1635ef45a</t>
+          <t>https://www.indeed.com/viewjob?jk=912b403391eebae1</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>IT Business Systems Analyst</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MTI Motion</t>
+          <t>Vforce Infotech</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Pleasant Prairie, WI, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Azure, Oracle, SQL Server, ELT, dbt, Power BI, Tableau, Jenkins, Docker, Jenkins</t>
+          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,24 +5431,24 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f6c2033564fadc5</t>
+          <t>https://www.indeed.com/viewjob?jk=7a4124e344d24526</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer (TypeScript/Python)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, ELT, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Medallion Architecture, GCP, Scala, Snowflake, dbt, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,24 +5466,24 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1108428f0442645f</t>
+          <t>https://www.indeed.com/viewjob?jk=8557217074c1d741</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer (TypeScript/Python)</t>
+          <t>Data Integration Engineer I</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>mPulse</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,34 +5491,34 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, ELT, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb5b3f8be39e2cf3</t>
+          <t>https://www.indeed.com/viewjob?jk=40b5249f2897ae6d</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer (TypeScript/Python)</t>
+          <t>Data Integration Engineer I</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>mPulse</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,34 +5526,34 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, ELT, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=626a3ca05c9e1497</t>
+          <t>https://www.indeed.com/viewjob?jk=565a928d60feb307</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer (TypeScript/Python)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,34 +5561,34 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, ELT, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, EMR, Athena, S3, Databricks, Spark, Scala, Snowflake, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=948876a952a5db1a</t>
+          <t>https://www.indeed.com/viewjob?jk=30987ecce424f169</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer (TypeScript/Python)</t>
+          <t>Senior Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Ｃollective</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5596,34 +5596,34 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, ELT, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, GCP, BigQuery, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df19aee9bab6697d</t>
+          <t>https://www.indeed.com/viewjob?jk=57341d2f2afa0500</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer (TypeScript/Python)</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Smile Partners USA</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Troy, MI, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5631,34 +5631,34 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, ELT, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10123b5be13e8cee</t>
+          <t>https://www.indeed.com/viewjob?jk=42652418f10ddaf6</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Enterprise Solution Architects - Irving</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5666,34 +5666,34 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, Power BI, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=866494264fa824bd</t>
+          <t>https://www.indeed.com/viewjob?jk=0c99631c2a979de0</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior Software Engineer, Identity</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Zeta Global</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5701,7 +5701,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Hive, Spark, Scala, Kafka, Snowflake, NoSQL, Data Modeling, ELT, Kubernetes</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -5711,24 +5711,24 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e73bbf40e88ece05</t>
+          <t>https://www.indeed.com/viewjob?jk=a2626f31a8519115</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Software Engineer - Legacy Applications &amp; Modernization</t>
+          <t>Senior Software Engineer, Identity</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>CSC Generation</t>
+          <t>Zeta Global</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5736,7 +5736,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker, pytest</t>
+          <t>AWS, Hive, Spark, Scala, Kafka, Snowflake, NoSQL, Data Modeling, ELT, Kubernetes</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -5746,24 +5746,24 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10fe6636f3653803</t>
+          <t>https://www.indeed.com/viewjob?jk=8127a1fdd36b3f92</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Data Security (SecuPi) Administrator</t>
+          <t>Senior Software Engineer, Identity</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>KeyBank</t>
+          <t>Zeta Global</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL</t>
+          <t>AWS, Hive, Spark, Scala, Kafka, Snowflake, NoSQL, Data Modeling, ELT, Kubernetes</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -5781,24 +5781,24 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7c21e4f363c4b33</t>
+          <t>https://www.indeed.com/viewjob?jk=d0c452b1635ef45a</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Data Security (SecuPi) Administrator</t>
+          <t>Data Scientist - Clinical Machine Learning &amp; Flow Cytometry</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>KeyBank</t>
+          <t>St. Jude Children's Research Hospital</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Brooklyn, OH, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL</t>
+          <t>AWS, RDS, Scala, NoSQL, Tableau, MLOps, Docker, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -5816,102 +5816,102 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dc6dc5d398c5e43</t>
+          <t>https://www.indeed.com/viewjob?jk=dc16153ffd80ac29</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Software Engineer III - Java/Spring Boot/Kafka</t>
+          <t>Full Stack Engineer - Dallas, TX</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, HDFS, Spark, Scala, Kafka, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=704df45d73edd23e</t>
+          <t>https://www.indeed.com/viewjob?jk=2090e6291d9af573</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Java AWS Software Engineer III</t>
+          <t>DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Optisources LLC</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, Scala, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Azure, Google Cloud Platform, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a2deb552df5368e</t>
+          <t>https://www.indeed.com/viewjob?jk=674588f252c63a1f</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Full Stack Software Engineer (TypeScript/Python)</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>nextPoint</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, ELT, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -5921,32 +5921,32 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28cb7e036c4cfede</t>
+          <t>https://www.indeed.com/viewjob?jk=1108428f0442645f</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Distinguished Engineer - AI/ML Engineering</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Vertex AI, Spark, Scala, Kafka, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, Power BI, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -5956,32 +5956,32 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22537756cead7b79</t>
+          <t>https://www.indeed.com/viewjob?jk=866494264fa824bd</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Software Engineer I- Enterprise AI Products</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -5991,207 +5991,207 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=287e2617edce5555</t>
+          <t>https://www.indeed.com/viewjob?jk=e73bbf40e88ece05</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Summer 2027 Intern – Enterprise Technology – Engineer (Software, Data, Infrastructure)</t>
+          <t>Full Stack Software Engineer (TypeScript/Python)</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>State Farm</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, MySQL, Power BI, Splunk, CI/CD, Maven, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, ELT, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f7927f3bdc5788a</t>
+          <t>https://www.indeed.com/viewjob?jk=cb5b3f8be39e2cf3</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Senior ML Operations Engineer</t>
+          <t>Full Stack Software Engineer (TypeScript/Python)</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Symbotic</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>RDS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, ELT, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=573ecddae507313b</t>
+          <t>https://www.indeed.com/viewjob?jk=626a3ca05c9e1497</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Advanced Software Engineer</t>
+          <t>Full Stack Software Engineer (TypeScript/Python)</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>AWS, Azure, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, ELT, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=813f3f55e6f0904d</t>
+          <t>https://www.indeed.com/viewjob?jk=948876a952a5db1a</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Solutions Architect – Data Analytics (Hybrid - Newport News, VA)</t>
+          <t>Full Stack Software Engineer (TypeScript/Python)</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Ferguson</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Newport News, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Databricks Lakehouse, Power BI, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, ELT, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74a88f1cd0bc4605</t>
+          <t>https://www.indeed.com/viewjob?jk=df19aee9bab6697d</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Software Engineer (Full Stack Developer) - Remote</t>
+          <t>Full Stack Software Engineer (TypeScript/Python)</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, ELT, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1ee89c82aaaecc5</t>
+          <t>https://www.indeed.com/viewjob?jk=10123b5be13e8cee</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer - Legacy Applications &amp; Modernization</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CSC Generation</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, Splunk, CI/CD</t>
+          <t>AWS, S3, RDS, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker, pytest</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -6201,19 +6201,19 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02ff6f6e6edf5293</t>
+          <t>https://www.indeed.com/viewjob?jk=10fe6636f3653803</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Sr Data Engineering Architect – Fraud Domain-5</t>
+          <t>Data Security (SecuPi) Administrator</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>KeyBank</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -6222,11 +6222,11 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -6236,32 +6236,32 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cc5633ac50e4a9c</t>
+          <t>https://www.indeed.com/viewjob?jk=d7c21e4f363c4b33</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Scientist - PXT Analytics</t>
+          <t>Data Security (SecuPi) Administrator</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>KeyBank</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Brooklyn, OH, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Apache Airflow</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -6271,24 +6271,24 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90dd2e7c995cb4c9</t>
+          <t>https://www.indeed.com/viewjob?jk=9dc6dc5d398c5e43</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Nakupuna Companies</t>
+          <t>nextPoint</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6296,34 +6296,34 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, Oracle, ETL, Power BI, Tableau, Azure DevOps, AKS</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=302f426881732dba</t>
+          <t>https://www.indeed.com/viewjob?jk=28cb7e036c4cfede</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Developer DBA</t>
+          <t>Senior Backend Engineer, Core Services</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Aeroflow Health</t>
+          <t>Ellipsis Health</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Asheville, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6331,7 +6331,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -6341,32 +6341,32 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0ad833078dc9770</t>
+          <t>https://www.indeed.com/viewjob?jk=fb104c65d5c051e4</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Digital Native Business</t>
+          <t>DevOps &amp; AI Engineering Intern (Undergraduate)</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>WEX Inc.</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, MLOps, CI/CD</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Scala, CI/CD, GitHub Actions, Maven, Terraform</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -6376,32 +6376,32 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16a69c90e7b8f72f</t>
+          <t>https://www.indeed.com/viewjob?jk=b556599daea77b24</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Digital Native Business</t>
+          <t>Distinguished Engineer - AI/ML Engineering</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Verizon</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>West, TX, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, MLOps, CI/CD</t>
+          <t>AWS, RDS, GCP, BigQuery, Vertex AI, Spark, Scala, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -6411,32 +6411,32 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3a9ebb96d2c59a5</t>
+          <t>https://www.indeed.com/viewjob?jk=22537756cead7b79</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Digital Native Business</t>
+          <t>Software Engineer I- Enterprise AI Products</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -6446,102 +6446,102 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f996d189fabe2c4</t>
+          <t>https://www.indeed.com/viewjob?jk=287e2617edce5555</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Digital Native Business</t>
+          <t>Development Engineer</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Power Systems MFG., LLC</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jupiter, FL, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, MLOps, CI/CD</t>
+          <t>AWS, Lambda, S3, IAM, NoSQL, Data Modeling, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3995fc6eb8f81df6</t>
+          <t>https://www.indeed.com/viewjob?jk=0c4817632c304bcf</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Data Engineer L4 (Remote)</t>
+          <t>Senior DevOps Engineer (hybrid)</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Frontdoor</t>
+          <t>Johnson Controls</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>York, PA, US USA</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hadoop, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Event Hubs, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a9b135a0413894f</t>
+          <t>https://www.indeed.com/viewjob?jk=e5c9672421189d7f</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Data Platform DevOps Engineer - Senior Associate (Enterprise Data Solutions)</t>
+          <t>Summer 2027 Intern – Enterprise Technology – Engineer (Software, Data, Infrastructure)</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>State Farm</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Kafka, CI/CD, Jenkins, Jenkins, Git, Python</t>
+          <t>AWS, Lambda, RDS, MySQL, Power BI, Splunk, CI/CD, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -6551,32 +6551,32 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07de84eaf7866caf</t>
+          <t>https://www.indeed.com/viewjob?jk=0f7927f3bdc5788a</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Software Engineer III-ETL/PySpark</t>
+          <t>Solutions Architect – Data Analytics (Hybrid - Newport News, VA)</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Ferguson</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Newport News, VA, US USA</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, ETL, dbt, CI/CD, Airflow</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Databricks Lakehouse, Power BI, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -6586,32 +6586,32 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea273207167a8ae8</t>
+          <t>https://www.indeed.com/viewjob?jk=74a88f1cd0bc4605</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Software Engineer II - Platform Engineer/Databricks</t>
+          <t>Sr Data Engineering Architect – Fraud Domain-5</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -6621,32 +6621,32 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44f0c4a1bfd9338a</t>
+          <t>https://www.indeed.com/viewjob?jk=9cc5633ac50e4a9c</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer</t>
+          <t>Senior Associate, Data Scientist - PXT Analytics</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Fiduciary Tech</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Scala, DynamoDB, Dimensional Modeling, ETL, Power BI, Tableau</t>
+          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -6656,32 +6656,32 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d12757dff686e33</t>
+          <t>https://www.indeed.com/viewjob?jk=90dd2e7c995cb4c9</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Software Engineer 2</t>
+          <t>Senior ML Operations Engineer</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Symbotic</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, CI/CD, Jenkins, Docker, Kubernetes, AKS</t>
+          <t>RDS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -6691,32 +6691,32 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cba7ca1e76e49f73</t>
+          <t>https://www.indeed.com/viewjob?jk=573ecddae507313b</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Full Stack Cloud Software Engineer</t>
+          <t>Advanced Software Engineer</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Custom Health</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, MySQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, Azure, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -6726,32 +6726,32 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dca5d2f6227a7f3d</t>
+          <t>https://www.indeed.com/viewjob?jk=813f3f55e6f0904d</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Senior Software Developer</t>
+          <t>Software Engineer (Full Stack Developer) - Remote</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>P17 Solutions LLC</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Egg Harbor Township, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>S3, IAM, RDS, Oracle, PostgreSQL, CI/CD, Maven, Docker, Git, Python</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -6761,32 +6761,32 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f241d5d943c65e9</t>
+          <t>https://www.indeed.com/viewjob?jk=c1ee89c82aaaecc5</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Texas Health and Human Services Commission</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D182" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Google Cloud Platform, Scala, Oracle, PostgreSQL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -6796,19 +6796,19 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47d37c2372a4bc58</t>
+          <t>https://www.indeed.com/viewjob?jk=02ff6f6e6edf5293</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>FiscalNote</t>
+          <t>Nakupuna Companies</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -6817,38 +6817,38 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>RDS, Scala, Polars, Snowflake, Data Modeling, dbt, Tableau, DataOps, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Snowflake, Oracle, ETL, Power BI, Tableau, Azure DevOps, AKS</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=492f33334022854d</t>
+          <t>https://www.indeed.com/viewjob?jk=302f426881732dba</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Senior Database Developer (SQL &amp; Databricks)</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Digital Native Business</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Rooms To Go</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Seffner, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -6856,34 +6856,34 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Databricks Lakehouse, SQL Server, PostgreSQL, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7291666cf90be22a</t>
+          <t>https://www.indeed.com/viewjob?jk=16a69c90e7b8f72f</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer III</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Digital Native Business</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>West, TX, US USA</t>
         </is>
       </c>
       <c r="D185" t="n">
@@ -6891,7 +6891,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -6901,24 +6901,24 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bccda3473d5c3eec</t>
+          <t>https://www.indeed.com/viewjob?jk=c3a9ebb96d2c59a5</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Senior Engineer - (Java/Software Development/AI) - Hybrid</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Digital Native Business</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D186" t="n">
@@ -6926,7 +6926,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -6936,24 +6936,24 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e9380fbd837d96f</t>
+          <t>https://www.indeed.com/viewjob?jk=6f996d189fabe2c4</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Software Engineer Professional, Financial Engineering</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Digital Native Business</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Freddie Mac</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D187" t="n">
@@ -6961,15 +6961,750 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, MLOps, CI/CD</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3995fc6eb8f81df6</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Data Engineer L4 (Remote)</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Frontdoor</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D188" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>AWS, RDS, GCP, Hadoop, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0a9b135a0413894f</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Data Platform DevOps Engineer - Senior Associate (Enterprise Data Solutions)</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D189" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>AWS, ECS, RDS, Scala, Kafka, CI/CD, Jenkins, Jenkins, Git, Python</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=07de84eaf7866caf</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Software Engineer III-ETL/PySpark</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Wilmington, DE, US USA</t>
+        </is>
+      </c>
+      <c r="D190" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, ETL, dbt, CI/CD, Airflow</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ea273207167a8ae8</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Platform Engineer/Databricks</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D191" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=44f0c4a1bfd9338a</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Solutions Architect - Nutanix Database Service</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Nutanix</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D192" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b5385371f7a5eb99</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Solutions Architect - Nutanix Database Service</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Nutanix</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D193" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ecabceae450ef29c</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Solutions Architect - Nutanix Database Service</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Nutanix</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D194" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=56eb2530b4ff7a40</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Solutions Architect - Nutanix Database Service</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Nutanix</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D195" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6433ae988372e060</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Solutions Architect - Nutanix Database Service</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Nutanix</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D196" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9b64e5c0767c818b</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Solutions Architect - Nutanix Database Service</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Nutanix</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D197" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d449ce9fd9801204</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Solutions Architect - Nutanix Database Service</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Nutanix</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D198" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=15ec3a99ef9a9bf9</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Solutions Architect - Nutanix Database Service</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Nutanix</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D199" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=14d02a049bdb55f2</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Business Intelligence Engineer</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Fiduciary Tech</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D200" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, S3, RDS, Scala, DynamoDB, Dimensional Modeling, ETL, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0d12757dff686e33</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Software Engineer 2</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>U.S. Bank</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Irvine, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D201" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, CI/CD, Jenkins, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cba7ca1e76e49f73</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Senior Software Developer</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>P17 Solutions LLC</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Egg Harbor Township, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D202" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>S3, IAM, RDS, Oracle, PostgreSQL, CI/CD, Maven, Docker, Git, Python</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9f241d5d943c65e9</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer I, Full Stack</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Wpromote, LLC</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D203" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>AWS, RDS, GCP, Scala, PostgreSQL, Data Modeling, CI/CD, GitHub Actions, Kubernetes, pytest</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c05c7ecac6958717</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Java Developer</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Texas Health and Human Services Commission</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D204" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, Google Cloud Platform, Scala, Oracle, PostgreSQL, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=47d37c2372a4bc58</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>FiscalNote</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D205" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Polars, Snowflake, Data Modeling, dbt, Tableau, DataOps, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=492f33334022854d</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Business Intelligence Reporting/ Web Developer</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>SS&amp;C</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D206" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Dataflow, SQL Server, Data Modeling, Star Schema, ETL, REST API integration, Power BI</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8a5b4b90a50d5e15</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Senior Engineer - (Java/Software Development/AI) - Hybrid</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D207" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Docker</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8e9380fbd837d96f</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Software Engineer Professional, Financial Engineering</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Freddie Mac</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D208" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
           <t>AWS, RDS, Spark, PySpark, Scala, MySQL, Jenkins, Docker, Jenkins, Git</t>
         </is>
       </c>
-      <c r="F187" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="G187" t="inlineStr">
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=af8a3a5fe3ef71bb</t>
         </is>

--- a/results/job_matches_2026-09-15.xlsx
+++ b/results/job_matches_2026-09-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G208"/>
+  <dimension ref="A1:G219"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,7 +468,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Architect - Irving</t>
+          <t>Data Architect - Irving,TX</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AWS Python Data Engineer-6</t>
+          <t>Software Engineer III (Full Stack)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Sprouts Farmers Market</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, GCP, Scala, Kafka, SQL Server</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa471a4093b491aa</t>
+          <t>https://www.indeed.com/viewjob?jk=9717265e88692311</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Debt Solutions - San Diego, CA</t>
+          <t>AWS Python Data Engineer-6</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Medallion Architecture, BigQuery, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b158df89b8b4f2ba</t>
+          <t>https://www.indeed.com/viewjob?jk=aa471a4093b491aa</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer (Remote)</t>
+          <t>Senior Data Engineer - Debt Solutions - San Diego, CA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Quest Diagnostics</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Secaucus, NJ, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Synapse Analytics, Google Cloud Platform, GCP, BigQuery</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Medallion Architecture, BigQuery, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dca7148f734ca29b</t>
+          <t>https://www.indeed.com/viewjob?jk=b158df89b8b4f2ba</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Databrick Engineer</t>
+          <t>Data Engineer (Remote)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>TradeWind Services</t>
+          <t>Quest Diagnostics</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Richland, WA, US USA</t>
+          <t>Secaucus, NJ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, SQL Server</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Synapse Analytics, Google Cloud Platform, GCP, BigQuery</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53e3a08c1c44bf91</t>
+          <t>https://www.indeed.com/viewjob?jk=dca7148f734ca29b</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Telemetry Data Infrastructure DevOps Software Engineer III</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, Redshift, Azure, Data Factory, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c634a2ea8b0b5dc</t>
+          <t>https://www.indeed.com/viewjob?jk=b69a57d634f44c20</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Engineer - Hyperscale Analytics</t>
+          <t>Senior Databrick Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Veeam Software</t>
+          <t>TradeWind Services</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Richland, WA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, HDFS, Spark, Scala</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f17632f11610e0ed</t>
+          <t>https://www.indeed.com/viewjob?jk=53e3a08c1c44bf91</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr. AI Data Engineer</t>
+          <t>Telemetry Data Infrastructure DevOps Software Engineer III</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Park Place Technologies</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Highland Heights, OH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Dataflow, Hadoop, Spark, Scala</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e8be741f2af4076</t>
+          <t>https://www.indeed.com/viewjob?jk=8c634a2ea8b0b5dc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Infrastructure DevOps Software Engineer III</t>
+          <t>Senior Engineer - Hyperscale Analytics</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Veeam Software</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, HDFS, Spark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c736424a6d7924ca</t>
+          <t>https://www.indeed.com/viewjob?jk=f17632f11610e0ed</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Azure Data Architect</t>
+          <t>Sr. AI Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Park Place Technologies</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Wilmington, NC, US USA</t>
+          <t>Highland Heights, OH, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Medallion Architecture, Spark, PySpark</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Dataflow, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7608d5894436a65d</t>
+          <t>https://www.indeed.com/viewjob?jk=1e8be741f2af4076</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr. DevSecOps Engineer</t>
+          <t>Infrastructure DevOps Software Engineer III</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>EBSCO Information Services</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7fe85eb12d0cac3</t>
+          <t>https://www.indeed.com/viewjob?jk=c736424a6d7924ca</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Integration Engineer II</t>
+          <t>Senior Azure Data Architect</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>mPulse</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Wilmington, NC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Scala, Snowflake, SQL Server, PostgreSQL, ETL, ELT, dbt</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Medallion Architecture, Spark, PySpark</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38b79b27689fa7f5</t>
+          <t>https://www.indeed.com/viewjob?jk=7608d5894436a65d</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,19 +916,19 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3463838e828923f</t>
+          <t>https://www.indeed.com/viewjob?jk=38b79b27689fa7f5</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Engineer</t>
+          <t>Data Integration Engineer II</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BCD</t>
+          <t>mPulse</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Scala, CI/CD</t>
+          <t>AWS, Redshift, S3, Scala, Snowflake, SQL Server, PostgreSQL, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d22b7b216664062</t>
+          <t>https://www.indeed.com/viewjob?jk=b3463838e828923f</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer II (Full Stack)</t>
+          <t>Senior AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>BCD</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Kafka, DynamoDB</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=262e7b6fb0562f09</t>
+          <t>https://www.indeed.com/viewjob?jk=4d22b7b216664062</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer II (Full Stack)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, Databricks, Medallion Architecture, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Kafka, DynamoDB</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a91e83e2437ff07f</t>
+          <t>https://www.indeed.com/viewjob?jk=262e7b6fb0562f09</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer-1</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, Scala, PostgreSQL, DynamoDB</t>
+          <t>AWS, Glue, EMR, S3, Databricks, Medallion Architecture, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27628c1d7944c002</t>
+          <t>https://www.indeed.com/viewjob?jk=a91e83e2437ff07f</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data Databricks, Python / Java</t>
+          <t>Senior Java Full Stack Developer-1</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, Scala, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76a3f3303ca4a1e8</t>
+          <t>https://www.indeed.com/viewjob?jk=27628c1d7944c002</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Life Sciences.AI</t>
+          <t>Software Engineer III - Big Data Databricks, Python / Java</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, GCP, BigQuery, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a2b7a80aec3b5d1</t>
+          <t>https://www.indeed.com/viewjob?jk=76a3f3303ca4a1e8</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer - AdTech</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d6a3b442efcc911</t>
+          <t>https://www.indeed.com/viewjob?jk=5b2fbc392614d709</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer - AdTech</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Core specialty</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, GCP, Scala, Snowflake, Data Modeling, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7398d2f9ab83a441</t>
+          <t>https://www.indeed.com/viewjob?jk=6af04b95cd5d2424</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer - AdTech</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Core specialty</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, GCP, Scala, Snowflake, Data Modeling, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b44d832238c13ae8</t>
+          <t>https://www.indeed.com/viewjob?jk=ac6261dc9e00bfa1</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Data Engineer - AdTech</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>clickhouse</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,147 +1256,147 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fa44fdea0190b34</t>
+          <t>https://www.indeed.com/viewjob?jk=ff27778f4a9c568b</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineer III - PySpark/AWS/Databricks</t>
+          <t>Senior Data Engineer - AdTech</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Wellesley, MA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12b2d3a25dd65381</t>
+          <t>https://www.indeed.com/viewjob?jk=3854c365175f4276</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Developer-Information Services Senior</t>
+          <t>Senior Data Engineer - AdTech</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Indiana University Health</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afda63d4c955805b</t>
+          <t>https://www.indeed.com/viewjob?jk=1dd7a6b30eff5d07</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer - AdTech</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Hylant</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8820ee81d8c77a67</t>
+          <t>https://www.indeed.com/viewjob?jk=f69e132dc9a962d0</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer - Life Sciences.AI</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Hylant</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Carmel, IN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, IAM, Azure, Databricks, GCP, BigQuery, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fb4b4b353eb8bc7</t>
+          <t>https://www.indeed.com/viewjob?jk=6a2b7a80aec3b5d1</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Hylant</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09c607a8a6e9e6e1</t>
+          <t>https://www.indeed.com/viewjob?jk=2d6a3b442efcc911</t>
         </is>
       </c>
     </row>
@@ -1453,20 +1453,20 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Hylant</t>
+          <t>Core specialty</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, GCP, Scala, Snowflake, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00deb545cdf8539e</t>
+          <t>https://www.indeed.com/viewjob?jk=7398d2f9ab83a441</t>
         </is>
       </c>
     </row>
@@ -1488,20 +1488,20 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Hylant</t>
+          <t>Core specialty</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, GCP, Scala, Snowflake, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f436c35b9293c1bb</t>
+          <t>https://www.indeed.com/viewjob?jk=b44d832238c13ae8</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Hylant</t>
+          <t>clickhouse</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Fort Wayne, IN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,94 +1546,94 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42fde78a8e52a847</t>
+          <t>https://www.indeed.com/viewjob?jk=7fa44fdea0190b34</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Hylant</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93f331567a1b25da</t>
+          <t>https://www.indeed.com/viewjob?jk=6e62ff1bbfe4e73a</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Specialist Solutions Architect - Data Engineering (Healthcare &amp; Life Sciences)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Hylant</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ecdb7549167f466</t>
+          <t>https://www.indeed.com/viewjob?jk=ee4a79d5875658d6</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Hylant</t>
+          <t>NextPower</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Independence, OH, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Data Modeling, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0157f56a6e27cad5</t>
+          <t>https://www.indeed.com/viewjob?jk=1000f4bc65203865</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer III - PySpark/AWS/Databricks</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Hylant</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Bloomington, IN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ced0409c76f4850</t>
+          <t>https://www.indeed.com/viewjob?jk=12b2d3a25dd65381</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Developer-Information Services Senior</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Hylant</t>
+          <t>Indiana University Health</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f97eb4b6c78e57e1</t>
+          <t>https://www.indeed.com/viewjob?jk=afda63d4c955805b</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=080ed824e7309c6d</t>
+          <t>https://www.indeed.com/viewjob?jk=8820ee81d8c77a67</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Carmel, IN, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e9941187a535d8b</t>
+          <t>https://www.indeed.com/viewjob?jk=0fb4b4b353eb8bc7</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Findlay, OH, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26792be3f1ce7d82</t>
+          <t>https://www.indeed.com/viewjob?jk=09c607a8a6e9e6e1</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40097b188627fc8f</t>
+          <t>https://www.indeed.com/viewjob?jk=00deb545cdf8539e</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=438fab27a54b95e5</t>
+          <t>https://www.indeed.com/viewjob?jk=f436c35b9293c1bb</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>Fort Wayne, IN, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c6e53394ba3aa7e</t>
+          <t>https://www.indeed.com/viewjob?jk=42fde78a8e52a847</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e32d13892fbf579</t>
+          <t>https://www.indeed.com/viewjob?jk=93f331567a1b25da</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c82bfdcacec2b79</t>
+          <t>https://www.indeed.com/viewjob?jk=1ecdb7549167f466</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>Independence, OH, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18104515e179e7ed</t>
+          <t>https://www.indeed.com/viewjob?jk=0157f56a6e27cad5</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Dunwoody, GA, US USA</t>
+          <t>Bloomington, IN, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d522390ab1db0241</t>
+          <t>https://www.indeed.com/viewjob?jk=1ced0409c76f4850</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ad72ad30f1ab368</t>
+          <t>https://www.indeed.com/viewjob?jk=f97eb4b6c78e57e1</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Carolina, PR, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be64c2d5635296ce</t>
+          <t>https://www.indeed.com/viewjob?jk=080ed824e7309c6d</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f694fd137783bdde</t>
+          <t>https://www.indeed.com/viewjob?jk=0e9941187a535d8b</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Findlay, OH, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=299f65eca357474b</t>
+          <t>https://www.indeed.com/viewjob?jk=26792be3f1ce7d82</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78155475e0b7db74</t>
+          <t>https://www.indeed.com/viewjob?jk=40097b188627fc8f</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fc3e569ad89e0eb</t>
+          <t>https://www.indeed.com/viewjob?jk=438fab27a54b95e5</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=614cf434248f98f7</t>
+          <t>https://www.indeed.com/viewjob?jk=7c6e53394ba3aa7e</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2629ad6556cbacf4</t>
+          <t>https://www.indeed.com/viewjob?jk=2e32d13892fbf579</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8218cb998a5c0151</t>
+          <t>https://www.indeed.com/viewjob?jk=8c82bfdcacec2b79</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01de0a106d50019f</t>
+          <t>https://www.indeed.com/viewjob?jk=18104515e179e7ed</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Carolina, PR, US USA</t>
+          <t>Dunwoody, GA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a08ea81549a22f9</t>
+          <t>https://www.indeed.com/viewjob?jk=d522390ab1db0241</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56c3823d88792143</t>
+          <t>https://www.indeed.com/viewjob?jk=3ad72ad30f1ab368</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>Carolina, PR, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a55c291dace4b53</t>
+          <t>https://www.indeed.com/viewjob?jk=be64c2d5635296ce</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b3cff0ccd0ca269</t>
+          <t>https://www.indeed.com/viewjob?jk=f694fd137783bdde</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fae7a2c2e6e1358</t>
+          <t>https://www.indeed.com/viewjob?jk=299f65eca357474b</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=016a658dc9ac3489</t>
+          <t>https://www.indeed.com/viewjob?jk=78155475e0b7db74</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc0d0f1f18eb8438</t>
+          <t>https://www.indeed.com/viewjob?jk=4fc3e569ad89e0eb</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47971bbc08557e3c</t>
+          <t>https://www.indeed.com/viewjob?jk=614cf434248f98f7</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bfcc94d4b3f34a6</t>
+          <t>https://www.indeed.com/viewjob?jk=2629ad6556cbacf4</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f49f733f65d11ed</t>
+          <t>https://www.indeed.com/viewjob?jk=8218cb998a5c0151</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8330457e7c7d4248</t>
+          <t>https://www.indeed.com/viewjob?jk=01de0a106d50019f</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Carolina, PR, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f90aa460666eb778</t>
+          <t>https://www.indeed.com/viewjob?jk=6a08ea81549a22f9</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6701998be316239a</t>
+          <t>https://www.indeed.com/viewjob?jk=56c3823d88792143</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d920562d203a185e</t>
+          <t>https://www.indeed.com/viewjob?jk=1a55c291dace4b53</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8aa55866530a52ff</t>
+          <t>https://www.indeed.com/viewjob?jk=1b3cff0ccd0ca269</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a565c5a09573c96</t>
+          <t>https://www.indeed.com/viewjob?jk=7fae7a2c2e6e1358</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Birmingham, MI, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea61995aa36120f0</t>
+          <t>https://www.indeed.com/viewjob?jk=016a658dc9ac3489</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=885e1f5bffaa36a1</t>
+          <t>https://www.indeed.com/viewjob?jk=dc0d0f1f18eb8438</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Dublin, OH, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77ba46a2cdbcf8ec</t>
+          <t>https://www.indeed.com/viewjob?jk=47971bbc08557e3c</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0101e7a2a0fedfa2</t>
+          <t>https://www.indeed.com/viewjob?jk=7bfcc94d4b3f34a6</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=570dfe76b557e2f0</t>
+          <t>https://www.indeed.com/viewjob?jk=3f49f733f65d11ed</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Elkhart, IN, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d348ebc076adb84</t>
+          <t>https://www.indeed.com/viewjob?jk=8330457e7c7d4248</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98d25fbfe90fcd1b</t>
+          <t>https://www.indeed.com/viewjob?jk=f90aa460666eb778</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13b85db8861d59de</t>
+          <t>https://www.indeed.com/viewjob?jk=6701998be316239a</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>HI, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ffc3524695bd37a</t>
+          <t>https://www.indeed.com/viewjob?jk=d920562d203a185e</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09d343f340846bb1</t>
+          <t>https://www.indeed.com/viewjob?jk=8aa55866530a52ff</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Toledo, OH, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86fe5a29c6f478bb</t>
+          <t>https://www.indeed.com/viewjob?jk=7a565c5a09573c96</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>Birmingham, MI, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a71a75a7a6f6ded</t>
+          <t>https://www.indeed.com/viewjob?jk=ea61995aa36120f0</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4822d68866185d6</t>
+          <t>https://www.indeed.com/viewjob?jk=885e1f5bffaa36a1</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Dublin, OH, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e8c551e853470e4</t>
+          <t>https://www.indeed.com/viewjob?jk=77ba46a2cdbcf8ec</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7b3b740adef358e</t>
+          <t>https://www.indeed.com/viewjob?jk=0101e7a2a0fedfa2</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28bf28a64e288c3c</t>
+          <t>https://www.indeed.com/viewjob?jk=570dfe76b557e2f0</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Clinical Data Analyst (Healthcare Analytics)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Tendo</t>
+          <t>Hylant</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Elkhart, IN, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, RDS, Azure, Databricks, Spark, PySpark</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee930887aa7df056</t>
+          <t>https://www.indeed.com/viewjob?jk=8d348ebc076adb84</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Engineer, Software (SWE) – GIA Platform</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Hylant</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e58133888b7ac460</t>
+          <t>https://www.indeed.com/viewjob?jk=98d25fbfe90fcd1b</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Platform Administrator (Databricks)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Nitka Technologies</t>
+          <t>Hylant</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, IAM, Databricks, Unity Catalog, Hive, Spark, Kafka, Time Travel</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=414be1be9d96afd0</t>
+          <t>https://www.indeed.com/viewjob?jk=13b85db8861d59de</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Engineer 1</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>Hylant</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>HI, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,32 +3681,32 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=759a4cfd65b3309c</t>
+          <t>https://www.indeed.com/viewjob?jk=5ffc3524695bd37a</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Software Engineer III - ML Model Delivery</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Hylant</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, ECS, RDS, Databricks, Spark, Scala, MLOps, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,32 +3716,32 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fc384810dc1e31d</t>
+          <t>https://www.indeed.com/viewjob?jk=09d343f340846bb1</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Data Scientist – Healthcare Analytics</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>Hylant</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Toledo, OH, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,32 +3751,32 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eeadc804a9484d0d</t>
+          <t>https://www.indeed.com/viewjob?jk=86fe5a29c6f478bb</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Data Scientist – Healthcare Analytics</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>Hylant</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,32 +3786,32 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a28368c599a0643</t>
+          <t>https://www.indeed.com/viewjob?jk=8a71a75a7a6f6ded</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Data Scientist – Healthcare Analytics</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>Hylant</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Richland, WA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,32 +3821,32 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=220fde5a7ab61250</t>
+          <t>https://www.indeed.com/viewjob?jk=b4822d68866185d6</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Data Scientist – Healthcare Analytics</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>Hylant</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,32 +3856,32 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34b1402bf6437dcd</t>
+          <t>https://www.indeed.com/viewjob?jk=1e8c551e853470e4</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Data Scientist – Healthcare Analytics</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>Hylant</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Clinton, MS, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,32 +3891,32 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f19c9e531ef55a20</t>
+          <t>https://www.indeed.com/viewjob?jk=f7b3b740adef358e</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Data Scientist – Healthcare Analytics</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>Hylant</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Fargo, ND, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,32 +3926,32 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c9e73c822f8844a</t>
+          <t>https://www.indeed.com/viewjob?jk=28bf28a64e288c3c</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Data Scientist – Healthcare Analytics</t>
+          <t>Snowflake Architect</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Annapolis, MD, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,32 +3961,32 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85c7d84effba6226</t>
+          <t>https://www.indeed.com/viewjob?jk=b59486981299cdc8</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Data Scientist – Healthcare Analytics</t>
+          <t>Platform Administrator (Databricks)</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>Nitka Technologies</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
+          <t>AWS, S3, SQS, IAM, Databricks, Unity Catalog, Hive, Spark, Kafka, Time Travel</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,32 +3996,32 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60c7d9e06cdaf076</t>
+          <t>https://www.indeed.com/viewjob?jk=414be1be9d96afd0</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Data Scientist – Healthcare Analytics</t>
+          <t>Senior Engineer, Software (SWE) – GIA Platform</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, CI/CD</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,32 +4031,32 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21f12a1ca162239a</t>
+          <t>https://www.indeed.com/viewjob?jk=e58133888b7ac460</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Data Scientist – Healthcare Analytics</t>
+          <t>Engineer 1</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Liberty, MO, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d94a40eeb0b40c06</t>
+          <t>https://www.indeed.com/viewjob?jk=759a4cfd65b3309c</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Data Scientist – Healthcare Analytics</t>
+          <t>Palantir Data Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Newmarket, NH, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6294f6e595512d42</t>
+          <t>https://www.indeed.com/viewjob?jk=846bf8f81216a75d</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Data Scientist – Healthcare Analytics</t>
+          <t>Software Engineer III - ML Model Delivery</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Monrovia, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
+          <t>AWS, EMR, S3, ECS, RDS, Databricks, Spark, Scala, MLOps, Terraform</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=885e9edc1afd7aa4</t>
+          <t>https://www.indeed.com/viewjob?jk=8fc384810dc1e31d</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25e0a7f11b2f5765</t>
+          <t>https://www.indeed.com/viewjob?jk=eeadc804a9484d0d</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80a579dae67397ca</t>
+          <t>https://www.indeed.com/viewjob?jk=9a28368c599a0643</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Richland, WA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5feacfc39b3d5f9a</t>
+          <t>https://www.indeed.com/viewjob?jk=220fde5a7ab61250</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Newport, MI, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d8a52daee3e8452</t>
+          <t>https://www.indeed.com/viewjob?jk=34b1402bf6437dcd</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Baton Rouge, LA, US USA</t>
+          <t>Clinton, MS, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0ed8e336465d87a</t>
+          <t>https://www.indeed.com/viewjob?jk=f19c9e531ef55a20</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Fargo, ND, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25a3d0fe6ce79647</t>
+          <t>https://www.indeed.com/viewjob?jk=2c9e73c822f8844a</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Medway, MA, US USA</t>
+          <t>Annapolis, MD, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f686962a348d2f1d</t>
+          <t>https://www.indeed.com/viewjob?jk=85c7d84effba6226</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Watson, AR, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4782d437ac23c24f</t>
+          <t>https://www.indeed.com/viewjob?jk=60c7d9e06cdaf076</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Marion, IA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4581f1a3af15cc3</t>
+          <t>https://www.indeed.com/viewjob?jk=21f12a1ca162239a</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Hudson, WI, US USA</t>
+          <t>Liberty, MO, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ed08d422e18d838</t>
+          <t>https://www.indeed.com/viewjob?jk=d94a40eeb0b40c06</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Newmarket, NH, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3d42ed3ce6788ed</t>
+          <t>https://www.indeed.com/viewjob?jk=6294f6e595512d42</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Barrington, RI, US USA</t>
+          <t>Monrovia, CA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54f7850a724e338c</t>
+          <t>https://www.indeed.com/viewjob?jk=885e9edc1afd7aa4</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b45d9f24f862a12b</t>
+          <t>https://www.indeed.com/viewjob?jk=25e0a7f11b2f5765</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Tyler, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=834a146cee4b0ee3</t>
+          <t>https://www.indeed.com/viewjob?jk=80a579dae67397ca</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Frankfort, KY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66bfe8bbf500669f</t>
+          <t>https://www.indeed.com/viewjob?jk=5feacfc39b3d5f9a</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Newport, MI, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b8778237b3a9a9b</t>
+          <t>https://www.indeed.com/viewjob?jk=7d8a52daee3e8452</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Honolulu, HI, US USA</t>
+          <t>Baton Rouge, LA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f5dfcba34d7a802</t>
+          <t>https://www.indeed.com/viewjob?jk=d0ed8e336465d87a</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Dayton, MN, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32f10a5c826d77c3</t>
+          <t>https://www.indeed.com/viewjob?jk=25a3d0fe6ce79647</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Medway, MA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1964898c1fe8582</t>
+          <t>https://www.indeed.com/viewjob?jk=f686962a348d2f1d</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Watson, AR, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5340ba338a6dbdb</t>
+          <t>https://www.indeed.com/viewjob?jk=4782d437ac23c24f</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Parlin, NJ, US USA</t>
+          <t>Marion, IA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04ad3829889eff15</t>
+          <t>https://www.indeed.com/viewjob?jk=e4581f1a3af15cc3</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Derby, CT, US USA</t>
+          <t>Hudson, WI, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee4a69c65915dae6</t>
+          <t>https://www.indeed.com/viewjob?jk=6ed08d422e18d838</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb5879047bb49aa2</t>
+          <t>https://www.indeed.com/viewjob?jk=f3d42ed3ce6788ed</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Barrington, RI, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=736a88fef080818b</t>
+          <t>https://www.indeed.com/viewjob?jk=54f7850a724e338c</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4914aa2faa0a7d7e</t>
+          <t>https://www.indeed.com/viewjob?jk=b45d9f24f862a12b</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Provo, UT, US USA</t>
+          <t>Tyler, TX, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09950965e6e09286</t>
+          <t>https://www.indeed.com/viewjob?jk=834a146cee4b0ee3</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Frankfort, KY, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc817f9191b34c97</t>
+          <t>https://www.indeed.com/viewjob?jk=66bfe8bbf500669f</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Caldwell, ID, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19ab03de0b3dc4f3</t>
+          <t>https://www.indeed.com/viewjob?jk=8b8778237b3a9a9b</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Pierre, SD, US USA</t>
+          <t>Honolulu, HI, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b7ac807f2bfd018</t>
+          <t>https://www.indeed.com/viewjob?jk=2f5dfcba34d7a802</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Rehoboth Beach, DE, US USA</t>
+          <t>Dayton, MN, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2998b67c6e643dc</t>
+          <t>https://www.indeed.com/viewjob?jk=32f10a5c826d77c3</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Stafford, VA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ee0e59c6632733f</t>
+          <t>https://www.indeed.com/viewjob?jk=c1964898c1fe8582</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Palmer, AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a89b194674200ed2</t>
+          <t>https://www.indeed.com/viewjob?jk=b5340ba338a6dbdb</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Parlin, NJ, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1e7316082fa5dfb</t>
+          <t>https://www.indeed.com/viewjob?jk=04ad3829889eff15</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Missoula, MT, US USA</t>
+          <t>Derby, CT, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=706b0b9e31c343c4</t>
+          <t>https://www.indeed.com/viewjob?jk=ee4a69c65915dae6</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf9c2207875eb310</t>
+          <t>https://www.indeed.com/viewjob?jk=cb5879047bb49aa2</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Data Scientist – Healthcare Analytics</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Cotulla Education</t>
+          <t>Ensora Health</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=912b403391eebae1</t>
+          <t>https://www.indeed.com/viewjob?jk=736a88fef080818b</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Scientist – Healthcare Analytics</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Vforce Infotech</t>
+          <t>Ensora Health</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,24 +5431,24 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a4124e344d24526</t>
+          <t>https://www.indeed.com/viewjob?jk=4914aa2faa0a7d7e</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Scientist – Healthcare Analytics</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>Ensora Health</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Provo, UT, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, GCP, Scala, Snowflake, dbt, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,24 +5466,24 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8557217074c1d741</t>
+          <t>https://www.indeed.com/viewjob?jk=09950965e6e09286</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Data Integration Engineer I</t>
+          <t>Senior Data Scientist – Healthcare Analytics</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>mPulse</t>
+          <t>Ensora Health</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5501,24 +5501,24 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40b5249f2897ae6d</t>
+          <t>https://www.indeed.com/viewjob?jk=cc817f9191b34c97</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Data Integration Engineer I</t>
+          <t>Senior Data Scientist – Healthcare Analytics</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>mPulse</t>
+          <t>Ensora Health</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Caldwell, ID, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5536,24 +5536,24 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=565a928d60feb307</t>
+          <t>https://www.indeed.com/viewjob?jk=19ab03de0b3dc4f3</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Data Scientist – Healthcare Analytics</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Ensora Health</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Pierre, SD, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AWS, EMR, Athena, S3, Databricks, Spark, Scala, Snowflake, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5571,24 +5571,24 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30987ecce424f169</t>
+          <t>https://www.indeed.com/viewjob?jk=6b7ac807f2bfd018</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Senior Cloud Infrastructure Engineer</t>
+          <t>Senior Data Scientist – Healthcare Analytics</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Ｃollective</t>
+          <t>Ensora Health</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Rehoboth Beach, DE, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, GCP, BigQuery, Scala, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5606,24 +5606,24 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57341d2f2afa0500</t>
+          <t>https://www.indeed.com/viewjob?jk=f2998b67c6e643dc</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Data Scientist – Healthcare Analytics</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Smile Partners USA</t>
+          <t>Ensora Health</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Troy, MI, US USA</t>
+          <t>Stafford, VA, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5631,34 +5631,34 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42652418f10ddaf6</t>
+          <t>https://www.indeed.com/viewjob?jk=1ee0e59c6632733f</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Enterprise Solution Architects - Irving</t>
+          <t>Senior Data Scientist – Healthcare Analytics</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Ensora Health</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Palmer, AK, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5666,34 +5666,34 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c99631c2a979de0</t>
+          <t>https://www.indeed.com/viewjob?jk=a89b194674200ed2</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Identity</t>
+          <t>Senior Data Scientist – Healthcare Analytics</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Zeta Global</t>
+          <t>Ensora Health</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5701,7 +5701,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>AWS, Hive, Spark, Scala, Kafka, Snowflake, NoSQL, Data Modeling, ELT, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -5711,24 +5711,24 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2626f31a8519115</t>
+          <t>https://www.indeed.com/viewjob?jk=e1e7316082fa5dfb</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Identity</t>
+          <t>Senior Data Scientist – Healthcare Analytics</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Zeta Global</t>
+          <t>Ensora Health</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Missoula, MT, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5736,7 +5736,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>AWS, Hive, Spark, Scala, Kafka, Snowflake, NoSQL, Data Modeling, ELT, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -5746,24 +5746,24 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8127a1fdd36b3f92</t>
+          <t>https://www.indeed.com/viewjob?jk=706b0b9e31c343c4</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Identity</t>
+          <t>Senior Data Scientist – Healthcare Analytics</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Zeta Global</t>
+          <t>Ensora Health</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>AWS, Hive, Spark, Scala, Kafka, Snowflake, NoSQL, Data Modeling, ELT, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -5781,24 +5781,24 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0c452b1635ef45a</t>
+          <t>https://www.indeed.com/viewjob?jk=cf9c2207875eb310</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Data Scientist - Clinical Machine Learning &amp; Flow Cytometry</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>St. Jude Children's Research Hospital</t>
+          <t>Cotulla Education</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, NoSQL, Tableau, MLOps, Docker, Git, Python, SQL</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -5816,24 +5816,24 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc16153ffd80ac29</t>
+          <t>https://www.indeed.com/viewjob?jk=912b403391eebae1</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Full Stack Engineer - Dallas, TX</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Vforce Infotech</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5841,34 +5841,34 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker</t>
+          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2090e6291d9af573</t>
+          <t>https://www.indeed.com/viewjob?jk=7a4124e344d24526</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>DevSecOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Optisources LLC</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5876,34 +5876,34 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Medallion Architecture, GCP, Scala, Snowflake, dbt, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=674588f252c63a1f</t>
+          <t>https://www.indeed.com/viewjob?jk=8557217074c1d741</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer (TypeScript/Python)</t>
+          <t>Data Integration Engineer I</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>mPulse</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, ELT, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -5921,24 +5921,24 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1108428f0442645f</t>
+          <t>https://www.indeed.com/viewjob?jk=40b5249f2897ae6d</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Data Integration Engineer I</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>mPulse</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, Power BI, GitHub Actions, Azure DevOps, Docker</t>
+          <t>Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -5956,24 +5956,24 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=866494264fa824bd</t>
+          <t>https://www.indeed.com/viewjob?jk=565a928d60feb307</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5981,7 +5981,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, EMR, Athena, S3, Databricks, Spark, Scala, Snowflake, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -5991,24 +5991,24 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e73bbf40e88ece05</t>
+          <t>https://www.indeed.com/viewjob?jk=30987ecce424f169</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer (TypeScript/Python)</t>
+          <t>Senior Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Ｃollective</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6016,34 +6016,34 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, ELT, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, GCP, BigQuery, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb5b3f8be39e2cf3</t>
+          <t>https://www.indeed.com/viewjob?jk=57341d2f2afa0500</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer (TypeScript/Python)</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Smile Partners USA</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Troy, MI, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6051,34 +6051,34 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, ELT, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=626a3ca05c9e1497</t>
+          <t>https://www.indeed.com/viewjob?jk=42652418f10ddaf6</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer (TypeScript/Python)</t>
+          <t>Enterprise Solution Architects - Irving,TX</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6086,34 +6086,34 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, ELT, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=948876a952a5db1a</t>
+          <t>https://www.indeed.com/viewjob?jk=0c99631c2a979de0</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer (TypeScript/Python)</t>
+          <t>Senior Software Engineer, Identity</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Zeta Global</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6121,34 +6121,34 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, ELT, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Hive, Spark, Scala, Kafka, Snowflake, NoSQL, Data Modeling, ELT, Kubernetes</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df19aee9bab6697d</t>
+          <t>https://www.indeed.com/viewjob?jk=a2626f31a8519115</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer (TypeScript/Python)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6156,34 +6156,34 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, ELT, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, SQL Server, MySQL, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10123b5be13e8cee</t>
+          <t>https://www.indeed.com/viewjob?jk=eeb102790d16f532</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Software Engineer - Legacy Applications &amp; Modernization</t>
+          <t>Full Stack Engineer - Dallas, TX</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>CSC Generation</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6191,34 +6191,34 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker, pytest</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10fe6636f3653803</t>
+          <t>https://www.indeed.com/viewjob?jk=2090e6291d9af573</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Data Security (SecuPi) Administrator</t>
+          <t>DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>KeyBank</t>
+          <t>Optisources LLC</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6226,34 +6226,34 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL</t>
+          <t>AWS, Azure, Google Cloud Platform, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7c21e4f363c4b33</t>
+          <t>https://www.indeed.com/viewjob?jk=674588f252c63a1f</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Data Security (SecuPi) Administrator</t>
+          <t>Full Stack Software Engineer (TypeScript/Python)</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>KeyBank</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Brooklyn, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, ELT, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -6271,32 +6271,32 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dc6dc5d398c5e43</t>
+          <t>https://www.indeed.com/viewjob?jk=1108428f0442645f</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>nextPoint</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, Power BI, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -6306,32 +6306,32 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28cb7e036c4cfede</t>
+          <t>https://www.indeed.com/viewjob?jk=866494264fa824bd</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer, Core Services</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Ellipsis Health</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -6341,207 +6341,207 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb104c65d5c051e4</t>
+          <t>https://www.indeed.com/viewjob?jk=e73bbf40e88ece05</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>DevOps &amp; AI Engineering Intern (Undergraduate)</t>
+          <t>Full Stack Software Engineer (TypeScript/Python)</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>WEX Inc.</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Scala, CI/CD, GitHub Actions, Maven, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, ELT, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b556599daea77b24</t>
+          <t>https://www.indeed.com/viewjob?jk=cb5b3f8be39e2cf3</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Distinguished Engineer - AI/ML Engineering</t>
+          <t>Full Stack Software Engineer (TypeScript/Python)</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Vertex AI, Spark, Scala, Kafka, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, ELT, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22537756cead7b79</t>
+          <t>https://www.indeed.com/viewjob?jk=626a3ca05c9e1497</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Software Engineer I- Enterprise AI Products</t>
+          <t>Full Stack Software Engineer (TypeScript/Python)</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, ELT, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=287e2617edce5555</t>
+          <t>https://www.indeed.com/viewjob?jk=948876a952a5db1a</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Development Engineer</t>
+          <t>Full Stack Software Engineer (TypeScript/Python)</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Power Systems MFG., LLC</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Jupiter, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, NoSQL, Data Modeling, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, ELT, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c4817632c304bcf</t>
+          <t>https://www.indeed.com/viewjob?jk=df19aee9bab6697d</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (hybrid)</t>
+          <t>Full Stack Software Engineer (TypeScript/Python)</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Johnson Controls</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>York, PA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Event Hubs, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, ELT, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5c9672421189d7f</t>
+          <t>https://www.indeed.com/viewjob?jk=10123b5be13e8cee</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Summer 2027 Intern – Enterprise Technology – Engineer (Software, Data, Infrastructure)</t>
+          <t>Senior Software Engineer, Identity</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>State Farm</t>
+          <t>Zeta Global</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, MySQL, Power BI, Splunk, CI/CD, Maven, Terraform, Docker</t>
+          <t>AWS, Hive, Spark, Scala, Kafka, Snowflake, NoSQL, Data Modeling, ELT, Kubernetes</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -6551,32 +6551,32 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f7927f3bdc5788a</t>
+          <t>https://www.indeed.com/viewjob?jk=8127a1fdd36b3f92</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Solutions Architect – Data Analytics (Hybrid - Newport News, VA)</t>
+          <t>Senior Software Engineer, Identity</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Ferguson</t>
+          <t>Zeta Global</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Newport News, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Databricks Lakehouse, Power BI, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Hive, Spark, Scala, Kafka, Snowflake, NoSQL, Data Modeling, ELT, Kubernetes</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -6586,19 +6586,19 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74a88f1cd0bc4605</t>
+          <t>https://www.indeed.com/viewjob?jk=d0c452b1635ef45a</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Sr Data Engineering Architect – Fraud Domain-5</t>
+          <t>Data Security (SecuPi) Administrator</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>KeyBank</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -6607,11 +6607,11 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -6621,32 +6621,32 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cc5633ac50e4a9c</t>
+          <t>https://www.indeed.com/viewjob?jk=d7c21e4f363c4b33</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Scientist - PXT Analytics</t>
+          <t>Data Security (SecuPi) Administrator</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>KeyBank</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Brooklyn, OH, US USA</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Apache Airflow</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -6656,24 +6656,24 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90dd2e7c995cb4c9</t>
+          <t>https://www.indeed.com/viewjob?jk=9dc6dc5d398c5e43</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Senior ML Operations Engineer</t>
+          <t>AI &amp; Data Platform Engineering Intern (Undergraduate)</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Symbotic</t>
+          <t>WEX Inc.</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -6681,7 +6681,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>RDS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Scala, Snowflake, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -6691,24 +6691,24 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=573ecddae507313b</t>
+          <t>https://www.indeed.com/viewjob?jk=75bca6b36a764259</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Advanced Software Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>nextPoint</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -6716,7 +6716,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>AWS, Azure, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -6726,24 +6726,24 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=813f3f55e6f0904d</t>
+          <t>https://www.indeed.com/viewjob?jk=28cb7e036c4cfede</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Software Engineer (Full Stack Developer) - Remote</t>
+          <t>Senior DevOps Engineer (hybrid)</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Johnson Controls</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>York, PA, US USA</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -6751,34 +6751,34 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Event Hubs, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1ee89c82aaaecc5</t>
+          <t>https://www.indeed.com/viewjob?jk=e5c9672421189d7f</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Backend Engineer, Core Services</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Ellipsis Health</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -6786,7 +6786,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -6796,19 +6796,19 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02ff6f6e6edf5293</t>
+          <t>https://www.indeed.com/viewjob?jk=fb104c65d5c051e4</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst</t>
+          <t>DevOps &amp; AI Engineering Intern (Undergraduate)</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Nakupuna Companies</t>
+          <t>WEX Inc.</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -6821,42 +6821,42 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, Oracle, ETL, Power BI, Tableau, Azure DevOps, AKS</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Scala, CI/CD, GitHub Actions, Maven, Terraform</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=302f426881732dba</t>
+          <t>https://www.indeed.com/viewjob?jk=b556599daea77b24</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Digital Native Business</t>
+          <t>Distinguished Engineer - AI/ML Engineering</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Verizon</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, MLOps, CI/CD</t>
+          <t>AWS, RDS, GCP, BigQuery, Vertex AI, Spark, Scala, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -6866,67 +6866,67 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16a69c90e7b8f72f</t>
+          <t>https://www.indeed.com/viewjob?jk=22537756cead7b79</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Digital Native Business</t>
+          <t>Development Engineer</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Power Systems MFG., LLC</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>West, TX, US USA</t>
+          <t>Jupiter, FL, US USA</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, MLOps, CI/CD</t>
+          <t>AWS, Lambda, S3, IAM, NoSQL, Data Modeling, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3a9ebb96d2c59a5</t>
+          <t>https://www.indeed.com/viewjob?jk=0c4817632c304bcf</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Digital Native Business</t>
+          <t>Software Engineer I- Enterprise AI Products</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -6936,32 +6936,32 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f996d189fabe2c4</t>
+          <t>https://www.indeed.com/viewjob?jk=287e2617edce5555</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Digital Native Business</t>
+          <t>Senior ML Operations Engineer</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Symbotic</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, MLOps, CI/CD</t>
+          <t>RDS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -6971,32 +6971,32 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3995fc6eb8f81df6</t>
+          <t>https://www.indeed.com/viewjob?jk=573ecddae507313b</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Data Engineer L4 (Remote)</t>
+          <t>Advanced Software Engineer</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Frontdoor</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hadoop, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, Azure, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -7006,32 +7006,32 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a9b135a0413894f</t>
+          <t>https://www.indeed.com/viewjob?jk=813f3f55e6f0904d</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Data Platform DevOps Engineer - Senior Associate (Enterprise Data Solutions)</t>
+          <t>Solutions Architect – Data Analytics (Hybrid - Newport News, VA)</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Ferguson</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Newport News, VA, US USA</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Kafka, CI/CD, Jenkins, Jenkins, Git, Python</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Databricks Lakehouse, Power BI, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -7041,32 +7041,32 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07de84eaf7866caf</t>
+          <t>https://www.indeed.com/viewjob?jk=74a88f1cd0bc4605</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Software Engineer III-ETL/PySpark</t>
+          <t>Software Engineer (Full Stack Developer) - Remote</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, ETL, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -7076,32 +7076,32 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea273207167a8ae8</t>
+          <t>https://www.indeed.com/viewjob?jk=c1ee89c82aaaecc5</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Software Engineer II - Platform Engineer/Databricks</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D191" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -7111,129 +7111,129 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44f0c4a1bfd9338a</t>
+          <t>https://www.indeed.com/viewjob?jk=02ff6f6e6edf5293</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Solutions Architect - Nutanix Database Service</t>
+          <t>Sr Data Engineering Architect – Fraud Domain-5</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Nutanix</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D192" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5385371f7a5eb99</t>
+          <t>https://www.indeed.com/viewjob?jk=9cc5633ac50e4a9c</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Solutions Architect - Nutanix Database Service</t>
+          <t>Senior Associate, Data Scientist - PXT Analytics</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Nutanix</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D193" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform</t>
+          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecabceae450ef29c</t>
+          <t>https://www.indeed.com/viewjob?jk=90dd2e7c995cb4c9</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Solutions Architect - Nutanix Database Service</t>
+          <t>Summer 2027 Intern – Enterprise Technology – Engineer (Software, Data, Infrastructure)</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Nutanix</t>
+          <t>State Farm</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D194" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform</t>
+          <t>AWS, Lambda, RDS, MySQL, Power BI, Splunk, CI/CD, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56eb2530b4ff7a40</t>
+          <t>https://www.indeed.com/viewjob?jk=0f7927f3bdc5788a</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Solutions Architect - Nutanix Database Service</t>
+          <t>Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Nutanix</t>
+          <t>Foot Locker</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D195" t="n">
@@ -7241,34 +7241,34 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, Snowflake, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6433ae988372e060</t>
+          <t>https://www.indeed.com/viewjob?jk=ba07136a4a72ee21</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Solutions Architect - Nutanix Database Service</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Digital Native Business</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Nutanix</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D196" t="n">
@@ -7276,34 +7276,34 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b64e5c0767c818b</t>
+          <t>https://www.indeed.com/viewjob?jk=16a69c90e7b8f72f</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Solutions Architect - Nutanix Database Service</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Digital Native Business</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Nutanix</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>West, TX, US USA</t>
         </is>
       </c>
       <c r="D197" t="n">
@@ -7311,34 +7311,34 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d449ce9fd9801204</t>
+          <t>https://www.indeed.com/viewjob?jk=c3a9ebb96d2c59a5</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Solutions Architect - Nutanix Database Service</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Digital Native Business</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Nutanix</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D198" t="n">
@@ -7346,34 +7346,34 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15ec3a99ef9a9bf9</t>
+          <t>https://www.indeed.com/viewjob?jk=6f996d189fabe2c4</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Solutions Architect - Nutanix Database Service</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Digital Native Business</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Nutanix</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D199" t="n">
@@ -7381,34 +7381,34 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14d02a049bdb55f2</t>
+          <t>https://www.indeed.com/viewjob?jk=3995fc6eb8f81df6</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer</t>
+          <t>Data Engineer L4 (Remote)</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Fiduciary Tech</t>
+          <t>Frontdoor</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D200" t="n">
@@ -7416,7 +7416,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Scala, DynamoDB, Dimensional Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, GCP, Hadoop, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -7426,24 +7426,24 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d12757dff686e33</t>
+          <t>https://www.indeed.com/viewjob?jk=0a9b135a0413894f</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Software Engineer 2</t>
+          <t>Data Platform DevOps Engineer - Senior Associate (Enterprise Data Solutions)</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D201" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, CI/CD, Jenkins, Docker, Kubernetes, AKS</t>
+          <t>AWS, ECS, RDS, Scala, Kafka, CI/CD, Jenkins, Jenkins, Git, Python</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -7461,24 +7461,24 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cba7ca1e76e49f73</t>
+          <t>https://www.indeed.com/viewjob?jk=07de84eaf7866caf</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Senior Software Developer</t>
+          <t>Software Engineer III-ETL/PySpark</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>P17 Solutions LLC</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Egg Harbor Township, NJ, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D202" t="n">
@@ -7486,7 +7486,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>S3, IAM, RDS, Oracle, PostgreSQL, CI/CD, Maven, Docker, Git, Python</t>
+          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, ETL, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -7496,24 +7496,24 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f241d5d943c65e9</t>
+          <t>https://www.indeed.com/viewjob?jk=ea273207167a8ae8</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I, Full Stack</t>
+          <t>Software Engineer II - Platform Engineer/Databricks</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Wpromote, LLC</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D203" t="n">
@@ -7521,34 +7521,34 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, PostgreSQL, Data Modeling, CI/CD, GitHub Actions, Kubernetes, pytest</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c05c7ecac6958717</t>
+          <t>https://www.indeed.com/viewjob?jk=44f0c4a1bfd9338a</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Senior Software Engineer I, Full Stack</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Texas Health and Human Services Commission</t>
+          <t>Wpromote, LLC</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D204" t="n">
@@ -7556,34 +7556,34 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Google Cloud Platform, Scala, Oracle, PostgreSQL, Docker, Kubernetes</t>
+          <t>AWS, RDS, GCP, Scala, PostgreSQL, Data Modeling, CI/CD, GitHub Actions, Kubernetes, pytest</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47d37c2372a4bc58</t>
+          <t>https://www.indeed.com/viewjob?jk=c05c7ecac6958717</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Solutions Architect - Nutanix Database Service</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>FiscalNote</t>
+          <t>Nutanix</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D205" t="n">
@@ -7591,34 +7591,34 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>RDS, Scala, Polars, Snowflake, Data Modeling, dbt, Tableau, DataOps, CI/CD, Git</t>
+          <t>AWS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=492f33334022854d</t>
+          <t>https://www.indeed.com/viewjob?jk=b5385371f7a5eb99</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Business Intelligence Reporting/ Web Developer</t>
+          <t>Solutions Architect - Nutanix Database Service</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>Nutanix</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D206" t="n">
@@ -7626,34 +7626,34 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Dataflow, SQL Server, Data Modeling, Star Schema, ETL, REST API integration, Power BI</t>
+          <t>AWS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a5b4b90a50d5e15</t>
+          <t>https://www.indeed.com/viewjob?jk=ecabceae450ef29c</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Senior Engineer - (Java/Software Development/AI) - Hybrid</t>
+          <t>Solutions Architect - Nutanix Database Service</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Nutanix</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D207" t="n">
@@ -7661,34 +7661,34 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Docker</t>
+          <t>AWS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e9380fbd837d96f</t>
+          <t>https://www.indeed.com/viewjob?jk=56eb2530b4ff7a40</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Software Engineer Professional, Financial Engineering</t>
+          <t>Solutions Architect - Nutanix Database Service</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Freddie Mac</t>
+          <t>Nutanix</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D208" t="n">
@@ -7696,15 +7696,400 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
+          <t>AWS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6433ae988372e060</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Solutions Architect - Nutanix Database Service</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Nutanix</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D209" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9b64e5c0767c818b</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Solutions Architect - Nutanix Database Service</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Nutanix</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D210" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d449ce9fd9801204</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Solutions Architect - Nutanix Database Service</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Nutanix</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D211" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=15ec3a99ef9a9bf9</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Solutions Architect - Nutanix Database Service</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Nutanix</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D212" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=14d02a049bdb55f2</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Business Intelligence Engineer</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Fiduciary Tech</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D213" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, S3, RDS, Scala, DynamoDB, Dimensional Modeling, ETL, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0d12757dff686e33</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Software Engineer 2</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>U.S. Bank</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Irvine, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D214" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, CI/CD, Jenkins, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cba7ca1e76e49f73</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Java Developer</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Texas Health and Human Services Commission</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D215" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, Google Cloud Platform, Scala, Oracle, PostgreSQL, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=47d37c2372a4bc58</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Business Intelligence Reporting/ Web Developer</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>SS&amp;C</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D216" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Dataflow, SQL Server, Data Modeling, Star Schema, ETL, REST API integration, Power BI</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8a5b4b90a50d5e15</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>FiscalNote</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D217" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Polars, Snowflake, Data Modeling, dbt, Tableau, DataOps, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=492f33334022854d</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Senior Engineer - (Java/Software Development/AI) - Hybrid</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D218" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Docker</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8e9380fbd837d96f</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Software Engineer Professional, Financial Engineering</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Freddie Mac</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D219" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
           <t>AWS, RDS, Spark, PySpark, Scala, MySQL, Jenkins, Docker, Jenkins, Git</t>
         </is>
       </c>
-      <c r="F208" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="G208" t="inlineStr">
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=af8a3a5fe3ef71bb</t>
         </is>

--- a/results/job_matches_2026-09-15.xlsx
+++ b/results/job_matches_2026-09-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G219"/>
+  <dimension ref="A1:G208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Architect - Irving,TX</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Vdrive IT Solutions, Inc</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20.1</v>
+        <v>27.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Kafka</t>
+          <t>AWS, Glue, EMR, Redshift, S3, RDS, Azure, Data Factory, Databricks, Data Lake Storage</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,67 +496,67 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbe7b157eada5171</t>
+          <t>https://www.indeed.com/viewjob?jk=667cfa1dd76c2ddd</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer III (Full Stack)</t>
+          <t>Data Architect - Irving,TX</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Sprouts Farmers Market</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.8</v>
+        <v>20.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, GCP, Scala, Kafka, SQL Server</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9717265e88692311</t>
+          <t>https://www.indeed.com/viewjob?jk=bbe7b157eada5171</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AWS Python Data Engineer-6</t>
+          <t>Software Engineer III (Full Stack)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Sprouts Farmers Market</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, GCP, Scala, Kafka, SQL Server</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa471a4093b491aa</t>
+          <t>https://www.indeed.com/viewjob?jk=9717265e88692311</t>
         </is>
       </c>
     </row>
@@ -608,17 +608,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer (Remote)</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Quest Diagnostics</t>
+          <t>BankUnited</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Secaucus, NJ, US USA</t>
+          <t>Miami Lakes, FL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,34 +626,34 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Synapse Analytics, Google Cloud Platform, GCP, BigQuery</t>
+          <t>AWS, RDS, Hadoop, Hive, Impala, Scala, Oracle, SQL Server, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dca7148f734ca29b</t>
+          <t>https://www.indeed.com/viewjob?jk=cce5aca3307e7b11</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer (Remote)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Quest Diagnostics</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Secaucus, NJ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Data Factory, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Synapse Analytics, Google Cloud Platform, GCP, BigQuery</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b69a57d634f44c20</t>
+          <t>https://www.indeed.com/viewjob?jk=dca7148f734ca29b</t>
         </is>
       </c>
     </row>
@@ -783,25 +783,25 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr. AI Data Engineer</t>
+          <t>Infrastructure DevOps Software Engineer III</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Park Place Technologies</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Highland Heights, OH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Dataflow, Hadoop, Spark, Scala</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e8be741f2af4076</t>
+          <t>https://www.indeed.com/viewjob?jk=c736424a6d7924ca</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Infrastructure DevOps Software Engineer III</t>
+          <t>Sr Software Engineer ( Gen AI)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Blue Yonder</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c736424a6d7924ca</t>
+          <t>https://www.indeed.com/viewjob?jk=9a55a27bf3bdffde</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Azure Data Architect</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Archer Technologies</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Wilmington, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,42 +871,42 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Medallion Architecture, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, ECS, RDS, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7608d5894436a65d</t>
+          <t>https://www.indeed.com/viewjob?jk=af675a1bad178e96</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Integration Engineer II</t>
+          <t>Senior Azure Data Architect</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>mPulse</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Wilmington, NC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Scala, Snowflake, SQL Server, PostgreSQL, ETL, ELT, dbt</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Medallion Architecture, Spark, PySpark</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38b79b27689fa7f5</t>
+          <t>https://www.indeed.com/viewjob?jk=7608d5894436a65d</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,19 +951,19 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3463838e828923f</t>
+          <t>https://www.indeed.com/viewjob?jk=38b79b27689fa7f5</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Engineer</t>
+          <t>Data Integration Engineer II</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BCD</t>
+          <t>mPulse</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Scala, CI/CD</t>
+          <t>AWS, Redshift, S3, Scala, Snowflake, SQL Server, PostgreSQL, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d22b7b216664062</t>
+          <t>https://www.indeed.com/viewjob?jk=b3463838e828923f</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer II (Full Stack)</t>
+          <t>Senior AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>BCD</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Kafka, DynamoDB</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=262e7b6fb0562f09</t>
+          <t>https://www.indeed.com/viewjob?jk=4d22b7b216664062</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer II (Full Stack)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, Databricks, Medallion Architecture, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Kafka, DynamoDB</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a91e83e2437ff07f</t>
+          <t>https://www.indeed.com/viewjob?jk=262e7b6fb0562f09</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer-1</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, Scala, PostgreSQL, DynamoDB</t>
+          <t>AWS, Glue, EMR, S3, Databricks, Medallion Architecture, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27628c1d7944c002</t>
+          <t>https://www.indeed.com/viewjob?jk=a91e83e2437ff07f</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data Databricks, Python / Java</t>
+          <t>Sr. Database Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>USA TODAY Co.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Redshift, SQS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76a3f3303ca4a1e8</t>
+          <t>https://www.indeed.com/viewjob?jk=89a64e47bb998b04</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - AdTech</t>
+          <t>Senior Solutions Architect</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>United Concordia Dental</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, GCP, BigQuery, Spark, Scala, dbt, Terraform</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b2fbc392614d709</t>
+          <t>https://www.indeed.com/viewjob?jk=fca9d1100abe83d1</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6af04b95cd5d2424</t>
+          <t>https://www.indeed.com/viewjob?jk=5b2fbc392614d709</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac6261dc9e00bfa1</t>
+          <t>https://www.indeed.com/viewjob?jk=6af04b95cd5d2424</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff27778f4a9c568b</t>
+          <t>https://www.indeed.com/viewjob?jk=ac6261dc9e00bfa1</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Wellesley, MA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3854c365175f4276</t>
+          <t>https://www.indeed.com/viewjob?jk=ff27778f4a9c568b</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Wellesley, MA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dd7a6b30eff5d07</t>
+          <t>https://www.indeed.com/viewjob?jk=3854c365175f4276</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f69e132dc9a962d0</t>
+          <t>https://www.indeed.com/viewjob?jk=1dd7a6b30eff5d07</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Life Sciences.AI</t>
+          <t>Senior Data Engineer - AdTech</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, GCP, BigQuery, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a2b7a80aec3b5d1</t>
+          <t>https://www.indeed.com/viewjob?jk=f69e132dc9a962d0</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer - Life Sciences.AI</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, IAM, Azure, Databricks, GCP, BigQuery, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d6a3b442efcc911</t>
+          <t>https://www.indeed.com/viewjob?jk=6a2b7a80aec3b5d1</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Core specialty</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, GCP, Scala, Snowflake, Data Modeling, ELT</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7398d2f9ab83a441</t>
+          <t>https://www.indeed.com/viewjob?jk=2d6a3b442efcc911</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Specialist Solutions Architect - Data Engineering (Healthcare &amp; Life Sciences)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Core specialty</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,42 +1501,42 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, GCP, Scala, Snowflake, Data Modeling, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b44d832238c13ae8</t>
+          <t>https://www.indeed.com/viewjob?jk=ee4a79d5875658d6</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>clickhouse</t>
+          <t>NextPower</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Data Modeling, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,94 +1546,94 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fa44fdea0190b34</t>
+          <t>https://www.indeed.com/viewjob?jk=1000f4bc65203865</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Hylant</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e62ff1bbfe4e73a</t>
+          <t>https://www.indeed.com/viewjob?jk=8820ee81d8c77a67</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Data Engineering (Healthcare &amp; Life Sciences)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Hylant</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Carmel, IN, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Scala, Spark Streaming</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee4a79d5875658d6</t>
+          <t>https://www.indeed.com/viewjob?jk=0fb4b4b353eb8bc7</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>NextPower</t>
+          <t>Hylant</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Data Modeling, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1000f4bc65203865</t>
+          <t>https://www.indeed.com/viewjob?jk=09c607a8a6e9e6e1</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Engineer III - PySpark/AWS/Databricks</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Hylant</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, CI/CD, Airflow</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12b2d3a25dd65381</t>
+          <t>https://www.indeed.com/viewjob?jk=00deb545cdf8539e</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Developer-Information Services Senior</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Indiana University Health</t>
+          <t>Hylant</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afda63d4c955805b</t>
+          <t>https://www.indeed.com/viewjob?jk=f436c35b9293c1bb</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Fort Wayne, IN, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8820ee81d8c77a67</t>
+          <t>https://www.indeed.com/viewjob?jk=42fde78a8e52a847</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Carmel, IN, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fb4b4b353eb8bc7</t>
+          <t>https://www.indeed.com/viewjob?jk=93f331567a1b25da</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09c607a8a6e9e6e1</t>
+          <t>https://www.indeed.com/viewjob?jk=1ecdb7549167f466</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>Independence, OH, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00deb545cdf8539e</t>
+          <t>https://www.indeed.com/viewjob?jk=0157f56a6e27cad5</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Bloomington, IN, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f436c35b9293c1bb</t>
+          <t>https://www.indeed.com/viewjob?jk=1ced0409c76f4850</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Fort Wayne, IN, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42fde78a8e52a847</t>
+          <t>https://www.indeed.com/viewjob?jk=f97eb4b6c78e57e1</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93f331567a1b25da</t>
+          <t>https://www.indeed.com/viewjob?jk=080ed824e7309c6d</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ecdb7549167f466</t>
+          <t>https://www.indeed.com/viewjob?jk=0e9941187a535d8b</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Independence, OH, US USA</t>
+          <t>Findlay, OH, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0157f56a6e27cad5</t>
+          <t>https://www.indeed.com/viewjob?jk=26792be3f1ce7d82</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bloomington, IN, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ced0409c76f4850</t>
+          <t>https://www.indeed.com/viewjob?jk=40097b188627fc8f</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f97eb4b6c78e57e1</t>
+          <t>https://www.indeed.com/viewjob?jk=438fab27a54b95e5</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=080ed824e7309c6d</t>
+          <t>https://www.indeed.com/viewjob?jk=7c6e53394ba3aa7e</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e9941187a535d8b</t>
+          <t>https://www.indeed.com/viewjob?jk=2e32d13892fbf579</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Findlay, OH, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26792be3f1ce7d82</t>
+          <t>https://www.indeed.com/viewjob?jk=8c82bfdcacec2b79</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40097b188627fc8f</t>
+          <t>https://www.indeed.com/viewjob?jk=18104515e179e7ed</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dunwoody, GA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=438fab27a54b95e5</t>
+          <t>https://www.indeed.com/viewjob?jk=d522390ab1db0241</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c6e53394ba3aa7e</t>
+          <t>https://www.indeed.com/viewjob?jk=3ad72ad30f1ab368</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>Carolina, PR, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e32d13892fbf579</t>
+          <t>https://www.indeed.com/viewjob?jk=be64c2d5635296ce</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c82bfdcacec2b79</t>
+          <t>https://www.indeed.com/viewjob?jk=f694fd137783bdde</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18104515e179e7ed</t>
+          <t>https://www.indeed.com/viewjob?jk=299f65eca357474b</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Dunwoody, GA, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d522390ab1db0241</t>
+          <t>https://www.indeed.com/viewjob?jk=78155475e0b7db74</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ad72ad30f1ab368</t>
+          <t>https://www.indeed.com/viewjob?jk=4fc3e569ad89e0eb</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Carolina, PR, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be64c2d5635296ce</t>
+          <t>https://www.indeed.com/viewjob?jk=614cf434248f98f7</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f694fd137783bdde</t>
+          <t>https://www.indeed.com/viewjob?jk=2629ad6556cbacf4</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=299f65eca357474b</t>
+          <t>https://www.indeed.com/viewjob?jk=8218cb998a5c0151</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78155475e0b7db74</t>
+          <t>https://www.indeed.com/viewjob?jk=01de0a106d50019f</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>Carolina, PR, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fc3e569ad89e0eb</t>
+          <t>https://www.indeed.com/viewjob?jk=6a08ea81549a22f9</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=614cf434248f98f7</t>
+          <t>https://www.indeed.com/viewjob?jk=56c3823d88792143</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2629ad6556cbacf4</t>
+          <t>https://www.indeed.com/viewjob?jk=1a55c291dace4b53</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8218cb998a5c0151</t>
+          <t>https://www.indeed.com/viewjob?jk=1b3cff0ccd0ca269</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01de0a106d50019f</t>
+          <t>https://www.indeed.com/viewjob?jk=7fae7a2c2e6e1358</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Carolina, PR, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a08ea81549a22f9</t>
+          <t>https://www.indeed.com/viewjob?jk=016a658dc9ac3489</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56c3823d88792143</t>
+          <t>https://www.indeed.com/viewjob?jk=dc0d0f1f18eb8438</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a55c291dace4b53</t>
+          <t>https://www.indeed.com/viewjob?jk=47971bbc08557e3c</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b3cff0ccd0ca269</t>
+          <t>https://www.indeed.com/viewjob?jk=7bfcc94d4b3f34a6</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fae7a2c2e6e1358</t>
+          <t>https://www.indeed.com/viewjob?jk=3f49f733f65d11ed</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=016a658dc9ac3489</t>
+          <t>https://www.indeed.com/viewjob?jk=8330457e7c7d4248</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc0d0f1f18eb8438</t>
+          <t>https://www.indeed.com/viewjob?jk=f90aa460666eb778</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47971bbc08557e3c</t>
+          <t>https://www.indeed.com/viewjob?jk=6701998be316239a</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bfcc94d4b3f34a6</t>
+          <t>https://www.indeed.com/viewjob?jk=d920562d203a185e</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f49f733f65d11ed</t>
+          <t>https://www.indeed.com/viewjob?jk=8aa55866530a52ff</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8330457e7c7d4248</t>
+          <t>https://www.indeed.com/viewjob?jk=7a565c5a09573c96</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Birmingham, MI, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f90aa460666eb778</t>
+          <t>https://www.indeed.com/viewjob?jk=ea61995aa36120f0</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6701998be316239a</t>
+          <t>https://www.indeed.com/viewjob?jk=885e1f5bffaa36a1</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Dublin, OH, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d920562d203a185e</t>
+          <t>https://www.indeed.com/viewjob?jk=77ba46a2cdbcf8ec</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8aa55866530a52ff</t>
+          <t>https://www.indeed.com/viewjob?jk=0101e7a2a0fedfa2</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a565c5a09573c96</t>
+          <t>https://www.indeed.com/viewjob?jk=570dfe76b557e2f0</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Birmingham, MI, US USA</t>
+          <t>Elkhart, IN, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea61995aa36120f0</t>
+          <t>https://www.indeed.com/viewjob?jk=8d348ebc076adb84</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=885e1f5bffaa36a1</t>
+          <t>https://www.indeed.com/viewjob?jk=98d25fbfe90fcd1b</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Dublin, OH, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77ba46a2cdbcf8ec</t>
+          <t>https://www.indeed.com/viewjob?jk=13b85db8861d59de</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>HI, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0101e7a2a0fedfa2</t>
+          <t>https://www.indeed.com/viewjob?jk=5ffc3524695bd37a</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=570dfe76b557e2f0</t>
+          <t>https://www.indeed.com/viewjob?jk=09d343f340846bb1</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Elkhart, IN, US USA</t>
+          <t>Toledo, OH, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d348ebc076adb84</t>
+          <t>https://www.indeed.com/viewjob?jk=86fe5a29c6f478bb</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98d25fbfe90fcd1b</t>
+          <t>https://www.indeed.com/viewjob?jk=8a71a75a7a6f6ded</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13b85db8861d59de</t>
+          <t>https://www.indeed.com/viewjob?jk=b4822d68866185d6</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>HI, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ffc3524695bd37a</t>
+          <t>https://www.indeed.com/viewjob?jk=1e8c551e853470e4</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09d343f340846bb1</t>
+          <t>https://www.indeed.com/viewjob?jk=f7b3b740adef358e</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Toledo, OH, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86fe5a29c6f478bb</t>
+          <t>https://www.indeed.com/viewjob?jk=28bf28a64e288c3c</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Hylant</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Lambda, S3, SNS, RDS, Databricks, Scala, Kafka, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a71a75a7a6f6ded</t>
+          <t>https://www.indeed.com/viewjob?jk=d8c55ab8d1ce73d1</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Snowflake Architect</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Hylant</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4822d68866185d6</t>
+          <t>https://www.indeed.com/viewjob?jk=b59486981299cdc8</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Engineer 1</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Hylant</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e8c551e853470e4</t>
+          <t>https://www.indeed.com/viewjob?jk=759a4cfd65b3309c</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Engineer, Software (SWE) – GIA Platform</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Hylant</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, CI/CD</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,32 +3891,32 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7b3b740adef358e</t>
+          <t>https://www.indeed.com/viewjob?jk=e58133888b7ac460</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Palantir Data Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Hylant</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,32 +3926,32 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28bf28a64e288c3c</t>
+          <t>https://www.indeed.com/viewjob?jk=846bf8f81216a75d</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Snowflake Architect</t>
+          <t>Software Engineer III - ML Model Delivery</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, EMR, S3, ECS, RDS, Databricks, Spark, Scala, MLOps, Terraform</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,32 +3961,32 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b59486981299cdc8</t>
+          <t>https://www.indeed.com/viewjob?jk=8fc384810dc1e31d</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Platform Administrator (Databricks)</t>
+          <t>Senior Data Scientist – Healthcare Analytics</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Nitka Technologies</t>
+          <t>Ensora Health</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, IAM, Databricks, Unity Catalog, Hive, Spark, Kafka, Time Travel</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,32 +3996,32 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=414be1be9d96afd0</t>
+          <t>https://www.indeed.com/viewjob?jk=eeadc804a9484d0d</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Engineer, Software (SWE) – GIA Platform</t>
+          <t>Senior Data Scientist – Healthcare Analytics</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Ensora Health</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,32 +4031,32 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e58133888b7ac460</t>
+          <t>https://www.indeed.com/viewjob?jk=9a28368c599a0643</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Engineer 1</t>
+          <t>Senior Data Scientist – Healthcare Analytics</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>Ensora Health</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Richland, WA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=759a4cfd65b3309c</t>
+          <t>https://www.indeed.com/viewjob?jk=220fde5a7ab61250</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Palantir Data Engineer</t>
+          <t>Senior Data Scientist – Healthcare Analytics</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Ensora Health</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=846bf8f81216a75d</t>
+          <t>https://www.indeed.com/viewjob?jk=34b1402bf6437dcd</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Software Engineer III - ML Model Delivery</t>
+          <t>Senior Data Scientist – Healthcare Analytics</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Ensora Health</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Clinton, MS, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, ECS, RDS, Databricks, Spark, Scala, MLOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fc384810dc1e31d</t>
+          <t>https://www.indeed.com/viewjob?jk=f19c9e531ef55a20</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Fargo, ND, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eeadc804a9484d0d</t>
+          <t>https://www.indeed.com/viewjob?jk=2c9e73c822f8844a</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Annapolis, MD, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a28368c599a0643</t>
+          <t>https://www.indeed.com/viewjob?jk=85c7d84effba6226</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Richland, WA, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=220fde5a7ab61250</t>
+          <t>https://www.indeed.com/viewjob?jk=60c7d9e06cdaf076</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34b1402bf6437dcd</t>
+          <t>https://www.indeed.com/viewjob?jk=21f12a1ca162239a</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Clinton, MS, US USA</t>
+          <t>Liberty, MO, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f19c9e531ef55a20</t>
+          <t>https://www.indeed.com/viewjob?jk=d94a40eeb0b40c06</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Fargo, ND, US USA</t>
+          <t>Newmarket, NH, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c9e73c822f8844a</t>
+          <t>https://www.indeed.com/viewjob?jk=6294f6e595512d42</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Annapolis, MD, US USA</t>
+          <t>Monrovia, CA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85c7d84effba6226</t>
+          <t>https://www.indeed.com/viewjob?jk=885e9edc1afd7aa4</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60c7d9e06cdaf076</t>
+          <t>https://www.indeed.com/viewjob?jk=25e0a7f11b2f5765</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21f12a1ca162239a</t>
+          <t>https://www.indeed.com/viewjob?jk=80a579dae67397ca</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Liberty, MO, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d94a40eeb0b40c06</t>
+          <t>https://www.indeed.com/viewjob?jk=5feacfc39b3d5f9a</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Newmarket, NH, US USA</t>
+          <t>Newport, MI, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6294f6e595512d42</t>
+          <t>https://www.indeed.com/viewjob?jk=7d8a52daee3e8452</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Monrovia, CA, US USA</t>
+          <t>Baton Rouge, LA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=885e9edc1afd7aa4</t>
+          <t>https://www.indeed.com/viewjob?jk=d0ed8e336465d87a</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25e0a7f11b2f5765</t>
+          <t>https://www.indeed.com/viewjob?jk=25a3d0fe6ce79647</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Medway, MA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80a579dae67397ca</t>
+          <t>https://www.indeed.com/viewjob?jk=f686962a348d2f1d</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Watson, AR, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5feacfc39b3d5f9a</t>
+          <t>https://www.indeed.com/viewjob?jk=4782d437ac23c24f</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Newport, MI, US USA</t>
+          <t>Marion, IA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d8a52daee3e8452</t>
+          <t>https://www.indeed.com/viewjob?jk=e4581f1a3af15cc3</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Baton Rouge, LA, US USA</t>
+          <t>Hudson, WI, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0ed8e336465d87a</t>
+          <t>https://www.indeed.com/viewjob?jk=6ed08d422e18d838</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25a3d0fe6ce79647</t>
+          <t>https://www.indeed.com/viewjob?jk=f3d42ed3ce6788ed</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Medway, MA, US USA</t>
+          <t>Barrington, RI, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f686962a348d2f1d</t>
+          <t>https://www.indeed.com/viewjob?jk=54f7850a724e338c</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Watson, AR, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4782d437ac23c24f</t>
+          <t>https://www.indeed.com/viewjob?jk=b45d9f24f862a12b</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Marion, IA, US USA</t>
+          <t>Tyler, TX, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4581f1a3af15cc3</t>
+          <t>https://www.indeed.com/viewjob?jk=834a146cee4b0ee3</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Hudson, WI, US USA</t>
+          <t>Frankfort, KY, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ed08d422e18d838</t>
+          <t>https://www.indeed.com/viewjob?jk=66bfe8bbf500669f</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3d42ed3ce6788ed</t>
+          <t>https://www.indeed.com/viewjob?jk=8b8778237b3a9a9b</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Barrington, RI, US USA</t>
+          <t>Honolulu, HI, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54f7850a724e338c</t>
+          <t>https://www.indeed.com/viewjob?jk=2f5dfcba34d7a802</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>Dayton, MN, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b45d9f24f862a12b</t>
+          <t>https://www.indeed.com/viewjob?jk=32f10a5c826d77c3</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Tyler, TX, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=834a146cee4b0ee3</t>
+          <t>https://www.indeed.com/viewjob?jk=c1964898c1fe8582</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Frankfort, KY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66bfe8bbf500669f</t>
+          <t>https://www.indeed.com/viewjob?jk=b5340ba338a6dbdb</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Parlin, NJ, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b8778237b3a9a9b</t>
+          <t>https://www.indeed.com/viewjob?jk=04ad3829889eff15</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Honolulu, HI, US USA</t>
+          <t>Derby, CT, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f5dfcba34d7a802</t>
+          <t>https://www.indeed.com/viewjob?jk=ee4a69c65915dae6</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Dayton, MN, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32f10a5c826d77c3</t>
+          <t>https://www.indeed.com/viewjob?jk=cb5879047bb49aa2</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1964898c1fe8582</t>
+          <t>https://www.indeed.com/viewjob?jk=736a88fef080818b</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5340ba338a6dbdb</t>
+          <t>https://www.indeed.com/viewjob?jk=4914aa2faa0a7d7e</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Parlin, NJ, US USA</t>
+          <t>Provo, UT, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04ad3829889eff15</t>
+          <t>https://www.indeed.com/viewjob?jk=09950965e6e09286</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Derby, CT, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee4a69c65915dae6</t>
+          <t>https://www.indeed.com/viewjob?jk=cc817f9191b34c97</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Caldwell, ID, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb5879047bb49aa2</t>
+          <t>https://www.indeed.com/viewjob?jk=19ab03de0b3dc4f3</t>
         </is>
       </c>
     </row>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Pierre, SD, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=736a88fef080818b</t>
+          <t>https://www.indeed.com/viewjob?jk=6b7ac807f2bfd018</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Rehoboth Beach, DE, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4914aa2faa0a7d7e</t>
+          <t>https://www.indeed.com/viewjob?jk=f2998b67c6e643dc</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Provo, UT, US USA</t>
+          <t>Stafford, VA, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09950965e6e09286</t>
+          <t>https://www.indeed.com/viewjob?jk=1ee0e59c6632733f</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Palmer, AK, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc817f9191b34c97</t>
+          <t>https://www.indeed.com/viewjob?jk=a89b194674200ed2</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Caldwell, ID, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19ab03de0b3dc4f3</t>
+          <t>https://www.indeed.com/viewjob?jk=e1e7316082fa5dfb</t>
         </is>
       </c>
     </row>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Pierre, SD, US USA</t>
+          <t>Missoula, MT, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b7ac807f2bfd018</t>
+          <t>https://www.indeed.com/viewjob?jk=706b0b9e31c343c4</t>
         </is>
       </c>
     </row>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Rehoboth Beach, DE, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5606,24 +5606,24 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2998b67c6e643dc</t>
+          <t>https://www.indeed.com/viewjob?jk=cf9c2207875eb310</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Senior Data Scientist – Healthcare Analytics</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>Cotulla Education</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Stafford, VA, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -5641,24 +5641,24 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ee0e59c6632733f</t>
+          <t>https://www.indeed.com/viewjob?jk=912b403391eebae1</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Senior Data Scientist – Healthcare Analytics</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>Vforce Infotech</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Palmer, AK, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
+          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -5676,24 +5676,24 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a89b194674200ed2</t>
+          <t>https://www.indeed.com/viewjob?jk=7a4124e344d24526</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Senior Data Scientist – Healthcare Analytics</t>
+          <t>Data Integration Engineer I</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>mPulse</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5701,7 +5701,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
+          <t>Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -5711,24 +5711,24 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1e7316082fa5dfb</t>
+          <t>https://www.indeed.com/viewjob?jk=40b5249f2897ae6d</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Senior Data Scientist – Healthcare Analytics</t>
+          <t>Data Integration Engineer I</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>mPulse</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Missoula, MT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5736,7 +5736,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
+          <t>Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -5746,24 +5746,24 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=706b0b9e31c343c4</t>
+          <t>https://www.indeed.com/viewjob?jk=565a928d60feb307</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Senior Data Scientist – Healthcare Analytics</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
+          <t>AWS, EMR, Athena, S3, Databricks, Spark, Scala, Snowflake, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -5781,24 +5781,24 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf9c2207875eb310</t>
+          <t>https://www.indeed.com/viewjob?jk=30987ecce424f169</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Cotulla Education</t>
+          <t>Ｃollective</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, GCP, BigQuery, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -5816,24 +5816,24 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=912b403391eebae1</t>
+          <t>https://www.indeed.com/viewjob?jk=57341d2f2afa0500</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Vforce Infotech</t>
+          <t>Smile Partners USA</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Troy, MI, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5841,34 +5841,34 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a4124e344d24526</t>
+          <t>https://www.indeed.com/viewjob?jk=42652418f10ddaf6</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Enterprise Solution Architects - Irving,TX</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5876,29 +5876,29 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, GCP, Scala, Snowflake, dbt, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8557217074c1d741</t>
+          <t>https://www.indeed.com/viewjob?jk=0c99631c2a979de0</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Data Integration Engineer I</t>
+          <t>Senior Software Engineer, Identity</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>mPulse</t>
+          <t>Zeta Global</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>AWS, Hive, Spark, Scala, Kafka, Snowflake, NoSQL, Data Modeling, ELT, Kubernetes</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -5921,24 +5921,24 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40b5249f2897ae6d</t>
+          <t>https://www.indeed.com/viewjob?jk=a2626f31a8519115</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Data Integration Engineer I</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>mPulse</t>
+          <t>Crane Worldwide Logistics</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5946,34 +5946,34 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>AWS, SQS, ECS, RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, ELT</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=565a928d60feb307</t>
+          <t>https://www.indeed.com/viewjob?jk=07af4f620d0cc3ad</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5981,34 +5981,34 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>AWS, EMR, Athena, S3, Databricks, Spark, Scala, Snowflake, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, SQL Server, MySQL, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30987ecce424f169</t>
+          <t>https://www.indeed.com/viewjob?jk=eeb102790d16f532</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Senior Cloud Infrastructure Engineer</t>
+          <t>Full Stack Engineer - Dallas, TX</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Ｃollective</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6016,34 +6016,34 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, GCP, BigQuery, Scala, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57341d2f2afa0500</t>
+          <t>https://www.indeed.com/viewjob?jk=2090e6291d9af573</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Smile Partners USA</t>
+          <t>Optisources LLC</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Troy, MI, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6051,34 +6051,34 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Google Cloud Platform, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42652418f10ddaf6</t>
+          <t>https://www.indeed.com/viewjob?jk=674588f252c63a1f</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Enterprise Solution Architects - Irving,TX</t>
+          <t>Full Stack Software Engineer (TypeScript/Python)</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6086,34 +6086,34 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, ELT, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c99631c2a979de0</t>
+          <t>https://www.indeed.com/viewjob?jk=1108428f0442645f</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Identity</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Zeta Global</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6121,7 +6121,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>AWS, Hive, Spark, Scala, Kafka, Snowflake, NoSQL, Data Modeling, ELT, Kubernetes</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, Power BI, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -6131,24 +6131,24 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2626f31a8519115</t>
+          <t>https://www.indeed.com/viewjob?jk=866494264fa824bd</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6156,34 +6156,34 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, SQL Server, MySQL, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eeb102790d16f532</t>
+          <t>https://www.indeed.com/viewjob?jk=e73bbf40e88ece05</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Full Stack Engineer - Dallas, TX</t>
+          <t>Full Stack Software Engineer (TypeScript/Python)</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6191,34 +6191,34 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, ELT, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2090e6291d9af573</t>
+          <t>https://www.indeed.com/viewjob?jk=cb5b3f8be39e2cf3</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>DevSecOps Engineer</t>
+          <t>Full Stack Software Engineer (TypeScript/Python)</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Optisources LLC</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6226,17 +6226,17 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, ELT, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=674588f252c63a1f</t>
+          <t>https://www.indeed.com/viewjob?jk=626a3ca05c9e1497</t>
         </is>
       </c>
     </row>
@@ -6253,7 +6253,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6266,29 +6266,29 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1108428f0442645f</t>
+          <t>https://www.indeed.com/viewjob?jk=948876a952a5db1a</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Full Stack Software Engineer (TypeScript/Python)</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6296,34 +6296,34 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, Power BI, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, ELT, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=866494264fa824bd</t>
+          <t>https://www.indeed.com/viewjob?jk=df19aee9bab6697d</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Full Stack Software Engineer (TypeScript/Python)</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6331,34 +6331,34 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, ELT, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e73bbf40e88ece05</t>
+          <t>https://www.indeed.com/viewjob?jk=10123b5be13e8cee</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer (TypeScript/Python)</t>
+          <t>Senior Software Engineer, Identity</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Zeta Global</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6366,34 +6366,34 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, ELT, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Hive, Spark, Scala, Kafka, Snowflake, NoSQL, Data Modeling, ELT, Kubernetes</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb5b3f8be39e2cf3</t>
+          <t>https://www.indeed.com/viewjob?jk=8127a1fdd36b3f92</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer (TypeScript/Python)</t>
+          <t>Senior Software Engineer, Identity</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Zeta Global</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -6401,34 +6401,34 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, ELT, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Hive, Spark, Scala, Kafka, Snowflake, NoSQL, Data Modeling, ELT, Kubernetes</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=626a3ca05c9e1497</t>
+          <t>https://www.indeed.com/viewjob?jk=d0c452b1635ef45a</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer (TypeScript/Python)</t>
+          <t>Data Security (SecuPi) Administrator</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>KeyBank</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6436,34 +6436,34 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, ELT, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=948876a952a5db1a</t>
+          <t>https://www.indeed.com/viewjob?jk=d7c21e4f363c4b33</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer (TypeScript/Python)</t>
+          <t>Data Security (SecuPi) Administrator</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>KeyBank</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Brooklyn, OH, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -6471,77 +6471,77 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, ELT, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df19aee9bab6697d</t>
+          <t>https://www.indeed.com/viewjob?jk=9dc6dc5d398c5e43</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer (TypeScript/Python)</t>
+          <t>AI &amp; Data Platform Engineering Intern (Undergraduate)</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>WEX Inc.</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, ELT, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Scala, Snowflake, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10123b5be13e8cee</t>
+          <t>https://www.indeed.com/viewjob?jk=75bca6b36a764259</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Identity</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Zeta Global</t>
+          <t>nextPoint</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>AWS, Hive, Spark, Scala, Kafka, Snowflake, NoSQL, Data Modeling, ELT, Kubernetes</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -6551,19 +6551,19 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8127a1fdd36b3f92</t>
+          <t>https://www.indeed.com/viewjob?jk=28cb7e036c4cfede</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Identity</t>
+          <t>Senior Backend Engineer, Core Services</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Zeta Global</t>
+          <t>Ellipsis Health</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -6572,11 +6572,11 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>AWS, Hive, Spark, Scala, Kafka, Snowflake, NoSQL, Data Modeling, ELT, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -6586,32 +6586,32 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0c452b1635ef45a</t>
+          <t>https://www.indeed.com/viewjob?jk=fb104c65d5c051e4</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Data Security (SecuPi) Administrator</t>
+          <t>DevOps &amp; AI Engineering Intern (Undergraduate)</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>KeyBank</t>
+          <t>WEX Inc.</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Scala, CI/CD, GitHub Actions, Maven, Terraform</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -6621,32 +6621,32 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7c21e4f363c4b33</t>
+          <t>https://www.indeed.com/viewjob?jk=b556599daea77b24</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Data Security (SecuPi) Administrator</t>
+          <t>Distinguished Engineer - AI/ML Engineering</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>KeyBank</t>
+          <t>Verizon</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Brooklyn, OH, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL</t>
+          <t>AWS, RDS, GCP, BigQuery, Vertex AI, Spark, Scala, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -6656,24 +6656,24 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dc6dc5d398c5e43</t>
+          <t>https://www.indeed.com/viewjob?jk=22537756cead7b79</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>AI &amp; Data Platform Engineering Intern (Undergraduate)</t>
+          <t>Development Engineer</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>WEX Inc.</t>
+          <t>Power Systems MFG., LLC</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jupiter, FL, US USA</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -6681,34 +6681,34 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Scala, Snowflake, dbt, CI/CD, Airflow</t>
+          <t>AWS, Lambda, S3, IAM, NoSQL, Data Modeling, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75bca6b36a764259</t>
+          <t>https://www.indeed.com/viewjob?jk=0c4817632c304bcf</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Solutions Architect – Data Analytics (Hybrid - Newport News, VA)</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>nextPoint</t>
+          <t>Ferguson</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Newport News, VA, US USA</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -6716,7 +6716,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Databricks Lakehouse, Power BI, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28cb7e036c4cfede</t>
+          <t>https://www.indeed.com/viewjob?jk=74a88f1cd0bc4605</t>
         </is>
       </c>
     </row>
@@ -6768,17 +6768,17 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer, Core Services</t>
+          <t>Software Engineer I- Enterprise AI Products</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Ellipsis Health</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -6786,7 +6786,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -6796,24 +6796,24 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb104c65d5c051e4</t>
+          <t>https://www.indeed.com/viewjob?jk=287e2617edce5555</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>DevOps &amp; AI Engineering Intern (Undergraduate)</t>
+          <t>Senior ML Operations Engineer</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>WEX Inc.</t>
+          <t>Symbotic</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D183" t="n">
@@ -6821,7 +6821,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Scala, CI/CD, GitHub Actions, Maven, Terraform</t>
+          <t>RDS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -6831,24 +6831,24 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b556599daea77b24</t>
+          <t>https://www.indeed.com/viewjob?jk=573ecddae507313b</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Distinguished Engineer - AI/ML Engineering</t>
+          <t>Advanced Software Engineer</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -6856,7 +6856,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Vertex AI, Spark, Scala, Kafka, MLOps, CI/CD</t>
+          <t>AWS, Azure, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -6866,24 +6866,24 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22537756cead7b79</t>
+          <t>https://www.indeed.com/viewjob?jk=813f3f55e6f0904d</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Development Engineer</t>
+          <t>Senior Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Power Systems MFG., LLC</t>
+          <t>AGILE FUEL</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Jupiter, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D185" t="n">
@@ -6891,34 +6891,34 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, NoSQL, Data Modeling, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MongoDB, NoSQL, ELT, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c4817632c304bcf</t>
+          <t>https://www.indeed.com/viewjob?jk=c7226137c575620c</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Software Engineer I- Enterprise AI Products</t>
+          <t>Summer 2027 Intern – Enterprise Technology – Engineer (Software, Data, Infrastructure)</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>State Farm</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D186" t="n">
@@ -6926,7 +6926,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, RDS, MySQL, Power BI, Splunk, CI/CD, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -6936,32 +6936,32 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=287e2617edce5555</t>
+          <t>https://www.indeed.com/viewjob?jk=0f7927f3bdc5788a</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Senior ML Operations Engineer</t>
+          <t>Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Symbotic</t>
+          <t>Foot Locker</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>RDS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, Snowflake, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -6971,32 +6971,32 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=573ecddae507313b</t>
+          <t>https://www.indeed.com/viewjob?jk=ba07136a4a72ee21</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Advanced Software Engineer</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Digital Native Business</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>AWS, Azure, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -7006,32 +7006,32 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=813f3f55e6f0904d</t>
+          <t>https://www.indeed.com/viewjob?jk=16a69c90e7b8f72f</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Solutions Architect – Data Analytics (Hybrid - Newport News, VA)</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Digital Native Business</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Ferguson</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Newport News, VA, US USA</t>
+          <t>West, TX, US USA</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Databricks Lakehouse, Power BI, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -7041,32 +7041,32 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74a88f1cd0bc4605</t>
+          <t>https://www.indeed.com/viewjob?jk=c3a9ebb96d2c59a5</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Software Engineer (Full Stack Developer) - Remote</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Digital Native Business</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -7076,32 +7076,32 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1ee89c82aaaecc5</t>
+          <t>https://www.indeed.com/viewjob?jk=6f996d189fabe2c4</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Digital Native Business</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D191" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -7111,32 +7111,32 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02ff6f6e6edf5293</t>
+          <t>https://www.indeed.com/viewjob?jk=3995fc6eb8f81df6</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Sr Data Engineering Architect – Fraud Domain-5</t>
+          <t>Data Engineer L4 (Remote)</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Frontdoor</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D192" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, GCP, Hadoop, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -7146,14 +7146,14 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cc5633ac50e4a9c</t>
+          <t>https://www.indeed.com/viewjob?jk=0a9b135a0413894f</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Scientist - PXT Analytics</t>
+          <t>Data Platform DevOps Engineer - Senior Associate (Enterprise Data Solutions)</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -7163,15 +7163,15 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D193" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Apache Airflow</t>
+          <t>AWS, ECS, RDS, Scala, Kafka, CI/CD, Jenkins, Jenkins, Git, Python</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -7181,59 +7181,59 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90dd2e7c995cb4c9</t>
+          <t>https://www.indeed.com/viewjob?jk=07de84eaf7866caf</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Summer 2027 Intern – Enterprise Technology – Engineer (Software, Data, Infrastructure)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>State Farm</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D194" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, MySQL, Power BI, Splunk, CI/CD, Maven, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Kafka, NoSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f7927f3bdc5788a</t>
+          <t>https://www.indeed.com/viewjob?jk=ad396daca54f6bd7</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Data &amp; Analytics Engineer</t>
+          <t>IT Architect - Cloud Platform</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Foot Locker</t>
+          <t>Maximus</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tysons, VA, US USA</t>
         </is>
       </c>
       <c r="D195" t="n">
@@ -7241,34 +7241,34 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, Snowflake, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Scala, ETL, Talend, CI/CD, Jenkins, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba07136a4a72ee21</t>
+          <t>https://www.indeed.com/viewjob?jk=e51855e99ddfa3fa</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Digital Native Business</t>
+          <t>Solutions Architect - Nutanix Database Service</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Nutanix</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D196" t="n">
@@ -7276,34 +7276,34 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, MLOps, CI/CD</t>
+          <t>AWS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16a69c90e7b8f72f</t>
+          <t>https://www.indeed.com/viewjob?jk=b5385371f7a5eb99</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Digital Native Business</t>
+          <t>Solutions Architect - Nutanix Database Service</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Nutanix</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>West, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D197" t="n">
@@ -7311,34 +7311,34 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, MLOps, CI/CD</t>
+          <t>AWS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3a9ebb96d2c59a5</t>
+          <t>https://www.indeed.com/viewjob?jk=ecabceae450ef29c</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Digital Native Business</t>
+          <t>Solutions Architect - Nutanix Database Service</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Nutanix</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D198" t="n">
@@ -7346,34 +7346,34 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, MLOps, CI/CD</t>
+          <t>AWS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f996d189fabe2c4</t>
+          <t>https://www.indeed.com/viewjob?jk=56eb2530b4ff7a40</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Digital Native Business</t>
+          <t>Solutions Architect - Nutanix Database Service</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Nutanix</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D199" t="n">
@@ -7381,34 +7381,34 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, MLOps, CI/CD</t>
+          <t>AWS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3995fc6eb8f81df6</t>
+          <t>https://www.indeed.com/viewjob?jk=6433ae988372e060</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Data Engineer L4 (Remote)</t>
+          <t>Solutions Architect - Nutanix Database Service</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Frontdoor</t>
+          <t>Nutanix</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D200" t="n">
@@ -7416,34 +7416,34 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hadoop, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a9b135a0413894f</t>
+          <t>https://www.indeed.com/viewjob?jk=9b64e5c0767c818b</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Data Platform DevOps Engineer - Senior Associate (Enterprise Data Solutions)</t>
+          <t>Solutions Architect - Nutanix Database Service</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Nutanix</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D201" t="n">
@@ -7451,34 +7451,34 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Kafka, CI/CD, Jenkins, Jenkins, Git, Python</t>
+          <t>AWS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07de84eaf7866caf</t>
+          <t>https://www.indeed.com/viewjob?jk=d449ce9fd9801204</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Software Engineer III-ETL/PySpark</t>
+          <t>Solutions Architect - Nutanix Database Service</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Nutanix</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D202" t="n">
@@ -7486,34 +7486,34 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, ETL, dbt, CI/CD, Airflow</t>
+          <t>AWS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea273207167a8ae8</t>
+          <t>https://www.indeed.com/viewjob?jk=15ec3a99ef9a9bf9</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Software Engineer II - Platform Engineer/Databricks</t>
+          <t>Solutions Architect - Nutanix Database Service</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Nutanix</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D203" t="n">
@@ -7521,34 +7521,34 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
+          <t>AWS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44f0c4a1bfd9338a</t>
+          <t>https://www.indeed.com/viewjob?jk=14d02a049bdb55f2</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I, Full Stack</t>
+          <t>Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Wpromote, LLC</t>
+          <t>Fiduciary Tech</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D204" t="n">
@@ -7556,34 +7556,34 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, PostgreSQL, Data Modeling, CI/CD, GitHub Actions, Kubernetes, pytest</t>
+          <t>AWS, Redshift, S3, RDS, Scala, DynamoDB, Dimensional Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c05c7ecac6958717</t>
+          <t>https://www.indeed.com/viewjob?jk=0d12757dff686e33</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Solutions Architect - Nutanix Database Service</t>
+          <t>Business Intelligence Reporting/ Web Developer</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Nutanix</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D205" t="n">
@@ -7591,34 +7591,34 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform</t>
+          <t>AWS, S3, RDS, Dataflow, SQL Server, Data Modeling, Star Schema, ETL, REST API integration, Power BI</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5385371f7a5eb99</t>
+          <t>https://www.indeed.com/viewjob?jk=8a5b4b90a50d5e15</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Solutions Architect - Nutanix Database Service</t>
+          <t>Software Engineer 2</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Nutanix</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D206" t="n">
@@ -7626,34 +7626,34 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, CI/CD, Jenkins, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecabceae450ef29c</t>
+          <t>https://www.indeed.com/viewjob?jk=cba7ca1e76e49f73</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Solutions Architect - Nutanix Database Service</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Nutanix</t>
+          <t>FiscalNote</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D207" t="n">
@@ -7661,34 +7661,34 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform</t>
+          <t>RDS, Scala, Polars, Snowflake, Data Modeling, dbt, Tableau, DataOps, CI/CD, Git</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56eb2530b4ff7a40</t>
+          <t>https://www.indeed.com/viewjob?jk=492f33334022854d</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Solutions Architect - Nutanix Database Service</t>
+          <t>Senior Engineer - (Java/Software Development/AI) - Hybrid</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Nutanix</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D208" t="n">
@@ -7696,402 +7696,17 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6433ae988372e060</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>Solutions Architect - Nutanix Database Service</t>
-        </is>
-      </c>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>Nutanix</t>
-        </is>
-      </c>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D209" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E209" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F209" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="G209" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9b64e5c0767c818b</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>Solutions Architect - Nutanix Database Service</t>
-        </is>
-      </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>Nutanix</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D210" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E210" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F210" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="G210" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d449ce9fd9801204</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>Solutions Architect - Nutanix Database Service</t>
-        </is>
-      </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>Nutanix</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D211" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E211" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F211" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="G211" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=15ec3a99ef9a9bf9</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>Solutions Architect - Nutanix Database Service</t>
-        </is>
-      </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>Nutanix</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D212" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E212" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F212" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="G212" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=14d02a049bdb55f2</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>Business Intelligence Engineer</t>
-        </is>
-      </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>Fiduciary Tech</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D213" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E213" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, S3, RDS, Scala, DynamoDB, Dimensional Modeling, ETL, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F213" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="G213" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0d12757dff686e33</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>Software Engineer 2</t>
-        </is>
-      </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>U.S. Bank</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>Irvine, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D214" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E214" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, CI/CD, Jenkins, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F214" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="G214" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cba7ca1e76e49f73</t>
-        </is>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>Java Developer</t>
-        </is>
-      </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>Texas Health and Human Services Commission</t>
-        </is>
-      </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D215" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E215" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, Google Cloud Platform, Scala, Oracle, PostgreSQL, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F215" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="G215" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=47d37c2372a4bc58</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="inlineStr">
-        <is>
-          <t>Business Intelligence Reporting/ Web Developer</t>
-        </is>
-      </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>SS&amp;C</t>
-        </is>
-      </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>Fort Worth, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D216" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E216" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Dataflow, SQL Server, Data Modeling, Star Schema, ETL, REST API integration, Power BI</t>
-        </is>
-      </c>
-      <c r="F216" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="G216" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8a5b4b90a50d5e15</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="inlineStr">
-        <is>
-          <t>Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>FiscalNote</t>
-        </is>
-      </c>
-      <c r="C217" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D217" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E217" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Polars, Snowflake, Data Modeling, dbt, Tableau, DataOps, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F217" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="G217" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=492f33334022854d</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="inlineStr">
-        <is>
-          <t>Senior Engineer - (Java/Software Development/AI) - Hybrid</t>
-        </is>
-      </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C218" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D218" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E218" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Docker</t>
-        </is>
-      </c>
-      <c r="F218" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="G218" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=8e9380fbd837d96f</t>
-        </is>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="inlineStr">
-        <is>
-          <t>Software Engineer Professional, Financial Engineering</t>
-        </is>
-      </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>Freddie Mac</t>
-        </is>
-      </c>
-      <c r="C219" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D219" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E219" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, MySQL, Jenkins, Docker, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F219" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="G219" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=af8a3a5fe3ef71bb</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-09-15.xlsx
+++ b/results/job_matches_2026-09-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G110"/>
+  <dimension ref="A1:G92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,17 +608,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Data Engineer - Debt Solutions - San Diego, CA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BankUnited</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Miami Lakes, FL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,34 +626,34 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, Impala, Scala, Oracle, SQL Server, MongoDB, Cassandra</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Medallion Architecture, BigQuery, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cce5aca3307e7b11</t>
+          <t>https://www.indeed.com/viewjob?jk=b158df89b8b4f2ba</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Debt Solutions - San Diego, CA</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>BankUnited</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Miami Lakes, FL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,17 +661,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Medallion Architecture, BigQuery, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Hadoop, Hive, Impala, Scala, Oracle, SQL Server, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b158df89b8b4f2ba</t>
+          <t>https://www.indeed.com/viewjob?jk=cce5aca3307e7b11</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Elsevier</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Glue, EMR, Lambda, S3, ECS, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93c4fe230bc9da32</t>
+          <t>https://www.indeed.com/viewjob?jk=0ec87e7c5d235465</t>
         </is>
       </c>
     </row>
@@ -753,7 +753,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>Elsevier</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2a3565a4a0f6c00</t>
+          <t>https://www.indeed.com/viewjob?jk=93c4fe230bc9da32</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Systems Engineer II</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56823350b0e43e7b</t>
+          <t>https://www.indeed.com/viewjob?jk=f2a3565a4a0f6c00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, ECS, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec87e7c5d235465</t>
+          <t>https://www.indeed.com/viewjob?jk=56823350b0e43e7b</t>
         </is>
       </c>
     </row>
@@ -888,52 +888,52 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Telemetry Data Infrastructure DevOps Software Engineer III</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Archer Technologies</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, ECS, RDS, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c634a2ea8b0b5dc</t>
+          <t>https://www.indeed.com/viewjob?jk=af675a1bad178e96</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Infrastructure DevOps Software Engineer III</t>
+          <t>Sr Software Engineer ( Gen AI)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Blue Yonder</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c736424a6d7924ca</t>
+          <t>https://www.indeed.com/viewjob?jk=9a55a27bf3bdffde</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Azure Data Architect</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Archer Technologies</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Wilmington, NC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,42 +976,42 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, ECS, RDS, Scala, PostgreSQL</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Medallion Architecture, Spark, PySpark</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af675a1bad178e96</t>
+          <t>https://www.indeed.com/viewjob?jk=7608d5894436a65d</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Azure Data Architect</t>
+          <t>Data Integration Engineer II</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>mPulse</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Wilmington, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Medallion Architecture, Spark, PySpark</t>
+          <t>AWS, Redshift, S3, Scala, Snowflake, SQL Server, PostgreSQL, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,59 +1021,59 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7608d5894436a65d</t>
+          <t>https://www.indeed.com/viewjob?jk=38b79b27689fa7f5</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr Software Engineer ( Gen AI)</t>
+          <t>Data Integration Engineer II</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Blue Yonder</t>
+          <t>mPulse</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, Redshift, S3, Scala, Snowflake, SQL Server, PostgreSQL, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a55a27bf3bdffde</t>
+          <t>https://www.indeed.com/viewjob?jk=b3463838e828923f</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Integration Engineer II</t>
+          <t>Analyst, Production Support</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>mPulse</t>
+          <t>Expion health</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,64 +1081,64 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Scala, Snowflake, SQL Server, PostgreSQL, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Scala, Snowflake, Time Travel, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38b79b27689fa7f5</t>
+          <t>https://www.indeed.com/viewjob?jk=249f623fa05a779f</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Integration Engineer II</t>
+          <t>Cloud Architect</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>mPulse</t>
+          <t>The Hearst Corporation</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Scala, Snowflake, SQL Server, PostgreSQL, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, API Gateway, ECS, IAM, RDS, Scala, MySQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3463838e828923f</t>
+          <t>https://www.indeed.com/viewjob?jk=ca46288b741312f0</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Engineer</t>
+          <t>Senior Data Scientist – Machine Learning &amp; AI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BCD</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1147,46 +1147,46 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Scala, CI/CD</t>
+          <t>AWS, Azure, GCP, Vertex AI, Spark, Scala, Snowflake, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d22b7b216664062</t>
+          <t>https://www.indeed.com/viewjob?jk=858b89b1e56571ed</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Cloud Architect</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>The Hearst Corporation</t>
+          <t>isolved</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, IAM, RDS, Scala, MySQL, DynamoDB, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,94 +1196,94 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca46288b741312f0</t>
+          <t>https://www.indeed.com/viewjob?jk=8b45e4d16b1cb423</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Engineer II (Full Stack)</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Mike Albert Leasing, Inc</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Kafka, DynamoDB</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=262e7b6fb0562f09</t>
+          <t>https://www.indeed.com/viewjob?jk=28ad3074a940aca6</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Solutions Architect</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>United Concordia Dental</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, Databricks, Medallion Architecture, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, GCP, BigQuery, Spark, Scala, dbt, Terraform</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a91e83e2437ff07f</t>
+          <t>https://www.indeed.com/viewjob?jk=fca9d1100abe83d1</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Sr. SW Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>isolved</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b45e4d16b1cb423</t>
+          <t>https://www.indeed.com/viewjob?jk=eeca57e502d5a7eb</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Trading Analytics Developer, Quantitative Trading</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Mike Albert Leasing, Inc</t>
+          <t>CRYPTO.com</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, MongoDB, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28ad3074a940aca6</t>
+          <t>https://www.indeed.com/viewjob?jk=2cfb2225c982e0d3</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr. Database Engineer</t>
+          <t>Trading Analytics Developer, Quantitative Trading</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>LocaliQ</t>
+          <t>CRYPTO.com</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, MongoDB, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13e3b070ab7cb4f9</t>
+          <t>https://www.indeed.com/viewjob?jk=be62e17c354b320c</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr. Database Engineer</t>
+          <t>Trading Analytics Developer, Quantitative Trading</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>LocaliQ</t>
+          <t>CRYPTO.com</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, MongoDB, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81d736c803ba352f</t>
+          <t>https://www.indeed.com/viewjob?jk=5c35d0114447fb50</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr. Database Engineer</t>
+          <t>2026016 - Software Engineer II (CA)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>USA TODAY Co.</t>
+          <t>John Deere</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Moline, IL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, PostgreSQL, MySQL</t>
+          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Spark, PostgreSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77dfcae90519cc06</t>
+          <t>https://www.indeed.com/viewjob?jk=5f2f62beea8bb80a</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sr. Database Engineer</t>
+          <t>Kubernetes Platform &amp; DevOps Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>USA TODAY Co.</t>
+          <t>Leidos</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Morgantown, WV, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, PostgreSQL, MySQL</t>
+          <t>AWS, S3, Azure, GCP, Kafka, PostgreSQL, MongoDB, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ad49a17e7017efb</t>
+          <t>https://www.indeed.com/viewjob?jk=82adbdad85a792ab</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Solutions Architect</t>
+          <t>Senior Data Engineer - AdTech</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>United Concordia Dental</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, GCP, BigQuery, Spark, Scala, dbt, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fca9d1100abe83d1</t>
+          <t>https://www.indeed.com/viewjob?jk=5b2fbc392614d709</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sr. SW Engineer</t>
+          <t>Senior Data Engineer - AdTech</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, Splunk, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eeca57e502d5a7eb</t>
+          <t>https://www.indeed.com/viewjob?jk=6af04b95cd5d2424</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Trading Analytics Developer, Quantitative Trading</t>
+          <t>Senior Data Engineer - AdTech</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CRYPTO.com</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, MongoDB, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cfb2225c982e0d3</t>
+          <t>https://www.indeed.com/viewjob?jk=ac6261dc9e00bfa1</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Trading Analytics Developer, Quantitative Trading</t>
+          <t>Senior Data Engineer - AdTech</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CRYPTO.com</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, MongoDB, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be62e17c354b320c</t>
+          <t>https://www.indeed.com/viewjob?jk=ff27778f4a9c568b</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Trading Analytics Developer, Quantitative Trading</t>
+          <t>Senior Data Engineer - AdTech</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CRYPTO.com</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Wellesley, MA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, MongoDB, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c35d0114447fb50</t>
+          <t>https://www.indeed.com/viewjob?jk=3854c365175f4276</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026016 - Software Engineer II (CA)</t>
+          <t>Senior Data Engineer - AdTech</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>John Deere</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Moline, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Spark, PostgreSQL, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f2f62beea8bb80a</t>
+          <t>https://www.indeed.com/viewjob?jk=1dd7a6b30eff5d07</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Kubernetes Platform &amp; DevOps Engineer</t>
+          <t>Senior Data Engineer - AdTech</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Leidos</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Morgantown, WV, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Kafka, PostgreSQL, MongoDB, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82adbdad85a792ab</t>
+          <t>https://www.indeed.com/viewjob?jk=f69e132dc9a962d0</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - AdTech</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Centene</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,77 +1746,77 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b2fbc392614d709</t>
+          <t>https://www.indeed.com/viewjob?jk=b48caf12e9a2d919</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - AdTech</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>NextPower</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Data Modeling, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6af04b95cd5d2424</t>
+          <t>https://www.indeed.com/viewjob?jk=1000f4bc65203865</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - AdTech</t>
+          <t>Sr. Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Halvik</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, S3, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac6261dc9e00bfa1</t>
+          <t>https://www.indeed.com/viewjob?jk=d4722e19a4c6bc57</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - AdTech</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>JELLYFISH</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, PySpark, Scala, Snowflake</t>
+          <t>IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, BigQuery, Spark, Scala, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff27778f4a9c568b</t>
+          <t>https://www.indeed.com/viewjob?jk=37ccdf3a9f7e654a</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - AdTech</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Wellesley, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,94 +1896,94 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3854c365175f4276</t>
+          <t>https://www.indeed.com/viewjob?jk=70157732c8210316</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - AdTech</t>
+          <t>Snowflake Architect</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dd7a6b30eff5d07</t>
+          <t>https://www.indeed.com/viewjob?jk=b59486981299cdc8</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - AdTech</t>
+          <t>Engineer 1</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f69e132dc9a962d0</t>
+          <t>https://www.indeed.com/viewjob?jk=759a4cfd65b3309c</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sr. Databricks Data Engineer</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Halvik</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, Lambda, S3, SNS, RDS, Databricks, Scala, Kafka, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4722e19a4c6bc57</t>
+          <t>https://www.indeed.com/viewjob?jk=d8c55ab8d1ce73d1</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Palantir Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>NextPower</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Data Modeling, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,102 +2036,102 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1000f4bc65203865</t>
+          <t>https://www.indeed.com/viewjob?jk=846bf8f81216a75d</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Snowflake Architect</t>
+          <t>Senior AWS Connect Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Modivcare</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b59486981299cdc8</t>
+          <t>https://www.indeed.com/viewjob?jk=ace77f8600c9c3a1</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Engineer 1</t>
+          <t>Senior AWS Connect Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>Modivcare</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=759a4cfd65b3309c</t>
+          <t>https://www.indeed.com/viewjob?jk=37fb83e9052e8c4f</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Engineer, Software (SWE) – GIA Platform</t>
+          <t>Data Integration Engineer I</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>mPulse</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, CI/CD</t>
+          <t>Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,67 +2141,67 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e58133888b7ac460</t>
+          <t>https://www.indeed.com/viewjob?jk=40b5249f2897ae6d</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Data Integration Engineer I</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>mPulse</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SNS, RDS, Databricks, Scala, Kafka, Snowflake, PostgreSQL</t>
+          <t>Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8c55ab8d1ce73d1</t>
+          <t>https://www.indeed.com/viewjob?jk=565a928d60feb307</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Engineer</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>VA Simplified</t>
+          <t>Astre Consulting Service Inc</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Kafka, NoSQL, CI/CD, GitHub Actions</t>
+          <t>Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2607541925dcfb86</t>
+          <t>https://www.indeed.com/viewjob?jk=8c930e89c4c66160</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Palantir Data Engineer</t>
+          <t>Software Development Engineer (DevOps)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=846bf8f81216a75d</t>
+          <t>https://www.indeed.com/viewjob?jk=da39e3bd2b6b4205</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Integration Engineer I</t>
+          <t>Software Development Engineer (DevOps)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>mPulse</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Vancouver, WA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40b5249f2897ae6d</t>
+          <t>https://www.indeed.com/viewjob?jk=e1f7d8bd9f99d822</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Integration Engineer I</t>
+          <t>Software Development Engineer (DevOps)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>mPulse</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,17 +2306,17 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=565a928d60feb307</t>
+          <t>https://www.indeed.com/viewjob?jk=a39b292b018429b6</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da39e3bd2b6b4205</t>
+          <t>https://www.indeed.com/viewjob?jk=300b116043f34bac</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Vancouver, WA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1f7d8bd9f99d822</t>
+          <t>https://www.indeed.com/viewjob?jk=be09b22adcb2fddf</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a39b292b018429b6</t>
+          <t>https://www.indeed.com/viewjob?jk=4cdf9d93c0ba359f</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=300b116043f34bac</t>
+          <t>https://www.indeed.com/viewjob?jk=666a4782fca49a28</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Development Engineer (DevOps)</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>Crane Worldwide Logistics</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, SQS, ECS, RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, ELT</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be09b22adcb2fddf</t>
+          <t>https://www.indeed.com/viewjob?jk=07af4f620d0cc3ad</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Development Engineer (DevOps)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, SQL Server, MySQL, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cdf9d93c0ba359f</t>
+          <t>https://www.indeed.com/viewjob?jk=eeb102790d16f532</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Development Engineer (DevOps)</t>
+          <t>Full Stack Engineer - Dallas, TX</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=666a4782fca49a28</t>
+          <t>https://www.indeed.com/viewjob?jk=2090e6291d9af573</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Enterprise Solution Architects - Irving,TX</t>
+          <t>DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Optisources LLC</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, Azure, Google Cloud Platform, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c99631c2a979de0</t>
+          <t>https://www.indeed.com/viewjob?jk=674588f252c63a1f</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Software Engineer II- Eng</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Astre Consulting Service Inc</t>
+          <t>UKG</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c930e89c4c66160</t>
+          <t>https://www.indeed.com/viewjob?jk=3e1fc3f1de5d21dc</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Quest Analytics Internship Program - Summer 2027 in Kansas City</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Crane Worldwide Logistics</t>
+          <t>Quest Analytics</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, SQS, ECS, RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, ELT</t>
+          <t>Databricks, Spark, SQL Server, MongoDB, NoSQL, ETL, ELT, Power BI, Git, Python</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07af4f620d0cc3ad</t>
+          <t>https://www.indeed.com/viewjob?jk=fa096b5f07acc65b</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>CG Infinity</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, SQL Server, MySQL, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, Redshift, Azure, GCP, Spark, Scala, Snowflake, Star Schema, Tableau, Git</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eeb102790d16f532</t>
+          <t>https://www.indeed.com/viewjob?jk=e06d6e56ef7c81de</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Full Stack Engineer - Dallas, TX</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>SquareTrade</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,312 +2736,312 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2090e6291d9af573</t>
+          <t>https://www.indeed.com/viewjob?jk=ba0a62a40f8906c0</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>DevSecOps Engineer</t>
+          <t>AI &amp; Data Platform Engineering Intern (Undergraduate)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Optisources LLC</t>
+          <t>WEX Inc.</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Scala, Snowflake, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=674588f252c63a1f</t>
+          <t>https://www.indeed.com/viewjob?jk=75bca6b36a764259</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer (TypeScript/Python)</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Palo Alto Networks</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, ELT, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>Google Cloud Platform, Hadoop, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1108428f0442645f</t>
+          <t>https://www.indeed.com/viewjob?jk=11f86cdd4c675439</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer (TypeScript/Python)</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>EarnIn</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, ELT, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Lambda, RDS, Scala, MLOps, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb5b3f8be39e2cf3</t>
+          <t>https://www.indeed.com/viewjob?jk=80f20f480a6626da</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer (TypeScript/Python)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Trimble</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Lake Oswego, OR, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, ELT, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>IAM, RDS, Azure, Scala, Kafka, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=626a3ca05c9e1497</t>
+          <t>https://www.indeed.com/viewjob?jk=b320160e6257e21f</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer (TypeScript/Python)</t>
+          <t>Senior DevOps Engineer (hybrid)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Johnson Controls</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>York, PA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, ELT, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Event Hubs, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=948876a952a5db1a</t>
+          <t>https://www.indeed.com/viewjob?jk=e5c9672421189d7f</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer (TypeScript/Python)</t>
+          <t>Senior Backend Engineer, Core Services</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Ellipsis Health</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, ELT, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df19aee9bab6697d</t>
+          <t>https://www.indeed.com/viewjob?jk=fb104c65d5c051e4</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer (TypeScript/Python)</t>
+          <t>DevOps &amp; AI Engineering Intern (Undergraduate)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>WEX Inc.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, ELT, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Scala, CI/CD, GitHub Actions, Maven, Terraform</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10123b5be13e8cee</t>
+          <t>https://www.indeed.com/viewjob?jk=b556599daea77b24</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Identity</t>
+          <t>AI &amp; Data Scientist Intern</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Zeta Global</t>
+          <t>Ingredion</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Westchester, IL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Hive, Spark, Scala, Kafka, Snowflake, NoSQL, Data Modeling, ELT, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2626f31a8519115</t>
+          <t>https://www.indeed.com/viewjob?jk=7e1b18d9ff34a767</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Quest Analytics Internship Program - Summer 2027 in Kansas City</t>
+          <t>AI &amp; Data Scientist Intern</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Quest Analytics</t>
+          <t>Ingredion</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Westchester, IL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Databricks, Spark, SQL Server, MongoDB, NoSQL, ETL, ELT, Power BI, Git, Python</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa096b5f07acc65b</t>
+          <t>https://www.indeed.com/viewjob?jk=222cf2907d848f0c</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Data Engineer, AI Enablement</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>EarnIn</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>North Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Scala, MLOps, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,67 +3086,67 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80f20f480a6626da</t>
+          <t>https://www.indeed.com/viewjob?jk=59419b9909aa5e8c</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>AI &amp; Data Platform Engineering Intern (Undergraduate)</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>WEX Inc.</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Temple, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Scala, Snowflake, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, ELT, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75bca6b36a764259</t>
+          <t>https://www.indeed.com/viewjob?jk=991793b1299304ff</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Applied Machine Learning Scientist II (AI/ML - Model Validation, GenAI &amp; Agentic AI)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SquareTrade</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, MLOps, MLflow, CI/CD, Git</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba0a62a40f8906c0</t>
+          <t>https://www.indeed.com/viewjob?jk=18a45300b5503869</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer, Core Services</t>
+          <t>Technology Development Program Associate - August 2027</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Ellipsis Health</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Python</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb104c65d5c051e4</t>
+          <t>https://www.indeed.com/viewjob?jk=718fa3c3e4a98b95</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>DevOps &amp; AI Engineering Intern (Undergraduate)</t>
+          <t>Senior Full Stack Developer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>WEX Inc.</t>
+          <t>Encore Global</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Schiller Park, IL, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Scala, CI/CD, GitHub Actions, Maven, Terraform</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,94 +3226,94 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b556599daea77b24</t>
+          <t>https://www.indeed.com/viewjob?jk=da71cda8fc390157</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Development Engineer</t>
+          <t>Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Power Systems MFG., LLC</t>
+          <t>Foot Locker</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Jupiter, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, NoSQL, Data Modeling, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, Snowflake, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c4817632c304bcf</t>
+          <t>https://www.indeed.com/viewjob?jk=ba07136a4a72ee21</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (hybrid)</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Digital Native Business</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Johnson Controls</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>York, PA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Event Hubs, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5c9672421189d7f</t>
+          <t>https://www.indeed.com/viewjob?jk=16a69c90e7b8f72f</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Engineer, AI Enablement</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Digital Native Business</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>North Chicago, IL, US USA</t>
+          <t>West, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59419b9909aa5e8c</t>
+          <t>https://www.indeed.com/viewjob?jk=c3a9ebb96d2c59a5</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Digital Native Business</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Temple, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, ELT, DataOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=991793b1299304ff</t>
+          <t>https://www.indeed.com/viewjob?jk=6f996d189fabe2c4</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Engineering Intern</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Digital Native Business</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>CAI (Computer Aid, Inc.)</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=448bed8907ce0072</t>
+          <t>https://www.indeed.com/viewjob?jk=3995fc6eb8f81df6</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data &amp; Analytics Engineer</t>
+          <t>Enterprise AI Systems Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Foot Locker</t>
+          <t>JUUL Labs</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, Snowflake, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, IAM, RDS, GCP, Vertex AI, Scala, Splunk, CI/CD, AKS, Git</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba07136a4a72ee21</t>
+          <t>https://www.indeed.com/viewjob?jk=90542e98749e2837</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>AI &amp; Data Scientist Intern</t>
+          <t>Data Engineering Intern</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Ingredion</t>
+          <t>CAI (Computer Aid, Inc.)</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Westchester, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e1b18d9ff34a767</t>
+          <t>https://www.indeed.com/viewjob?jk=448bed8907ce0072</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>AI &amp; Data Scientist Intern</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Ingredion</t>
+          <t>Trimble</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Westchester, IL, US USA</t>
+          <t>Lake Oswego, OR, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, NoSQL</t>
+          <t>IAM, RDS, Azure, Scala, Kafka, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=222cf2907d848f0c</t>
+          <t>https://www.indeed.com/viewjob?jk=af8c2d05083f261a</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Applied Machine Learning Scientist II (AI/ML - Model Validation, GenAI &amp; Agentic AI)</t>
+          <t>IT Architect - Cloud Platform</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>Maximus</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tysons, VA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, MLOps, MLflow, CI/CD, Git</t>
+          <t>AWS, IAM, RDS, Scala, ETL, Talend, CI/CD, Jenkins, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18a45300b5503869</t>
+          <t>https://www.indeed.com/viewjob?jk=e51855e99ddfa3fa</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Encore Global</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Schiller Park, IL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Kafka, NoSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da71cda8fc390157</t>
+          <t>https://www.indeed.com/viewjob?jk=ad396daca54f6bd7</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Digital Native Business</t>
+          <t>BI Report Developer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Topgolf</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, MLOps, CI/CD</t>
+          <t>AWS, Redshift, S3, RDS, Azure, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16a69c90e7b8f72f</t>
+          <t>https://www.indeed.com/viewjob?jk=b493a51345446a14</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Digital Native Business</t>
+          <t>Business Intelligence Reporting/ Web Developer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>West, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, MLOps, CI/CD</t>
+          <t>AWS, S3, RDS, Dataflow, SQL Server, Data Modeling, Star Schema, ETL, REST API integration, Power BI</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,637 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3a9ebb96d2c59a5</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Digital Native Business</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>CA, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, MLOps, CI/CD</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6f996d189fabe2c4</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Digital Native Business</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, MLOps, CI/CD</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3995fc6eb8f81df6</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>DEPLOY</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>AWS, SQS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=76b221e75a3ba5aa</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>IT Architect - Cloud Platform</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Maximus</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Tysons, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Scala, ETL, Talend, CI/CD, Jenkins, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e51855e99ddfa3fa</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Solutions Architect - Nutanix Database Service</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Nutanix</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b5385371f7a5eb99</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Solutions Architect - Nutanix Database Service</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Nutanix</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Miami, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ecabceae450ef29c</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Solutions Architect - Nutanix Database Service</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Nutanix</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=56eb2530b4ff7a40</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Solutions Architect - Nutanix Database Service</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Nutanix</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6433ae988372e060</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Solutions Architect - Nutanix Database Service</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Nutanix</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9b64e5c0767c818b</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Solutions Architect - Nutanix Database Service</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Nutanix</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d449ce9fd9801204</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Solutions Architect - Nutanix Database Service</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Nutanix</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=15ec3a99ef9a9bf9</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Solutions Architect - Nutanix Database Service</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Nutanix</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=14d02a049bdb55f2</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Optum</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Raleigh, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Kafka, NoSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ad396daca54f6bd7</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Software Engineer 2</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>U.S. Bank</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Irvine, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, CI/CD, Jenkins, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cba7ca1e76e49f73</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>FiscalNote</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Polars, Snowflake, Data Modeling, dbt, Tableau, DataOps, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=492f33334022854d</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>BI Report Developer</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Topgolf</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, S3, RDS, Azure, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b493a51345446a14</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Business Intelligence Reporting/ Web Developer</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>SS&amp;C</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Fort Worth, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Dataflow, SQL Server, Data Modeling, Star Schema, ETL, REST API integration, Power BI</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=8a5b4b90a50d5e15</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Software Development Engineer — Mobility Engineering</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>WEX Inc.</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>AWS, Scala, Kafka, Oracle, PostgreSQL, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=57bfdad1ac1598f5</t>
         </is>
       </c>
     </row>
